--- a/data/annual_loads_waterbodies.xlsx
+++ b/data/annual_loads_waterbodies.xlsx
@@ -4091,7 +4091,7 @@
         <v>1.09065538318044</v>
       </c>
       <c r="E169" t="n">
-        <v>441.1929326302305</v>
+        <v>302.743561619997</v>
       </c>
       <c r="F169" t="n">
         <v>260.8764771218694</v>
@@ -4110,7 +4110,7 @@
         <v>11.79403990597149</v>
       </c>
       <c r="D170" t="n">
-        <v>0.4490932839492897</v>
+        <v>0.3631692425541906</v>
       </c>
       <c r="E170" t="n">
         <v>131.4454693391129</v>
@@ -4157,7 +4157,7 @@
         <v>0.532714311779416</v>
       </c>
       <c r="E172" t="n">
-        <v>425.7667401549494</v>
+        <v>416.7633724753818</v>
       </c>
       <c r="F172" t="n">
         <v>192.2738714805733</v>
@@ -4196,7 +4196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4217,35 +4217,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>par</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>par</t>
+          <t>mk_trend</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>mk_trend</t>
+          <t>mk_pval</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>mk_pval</t>
+          <t>sslp</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>sslp</t>
+          <t>sslp_ub</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>sslp_ub</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>sslp_lb</t>
         </is>
@@ -4269,29 +4264,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>TOTN_tonn</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TOTN_tonn</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F2" t="n">
+        <v>0.2168604205660558</v>
+      </c>
       <c r="G2" t="n">
-        <v>0.2168604205660558</v>
+        <v>1.883447101247998</v>
       </c>
       <c r="H2" t="n">
-        <v>1.883447101247998</v>
+        <v>4.762377242521692</v>
       </c>
       <c r="I2" t="n">
-        <v>4.762377242521692</v>
-      </c>
-      <c r="J2" t="n">
         <v>-0.8951767848272653</v>
       </c>
     </row>
@@ -4313,29 +4303,24 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>TOTP_tonn</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TOTP_tonn</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F3" t="n">
+        <v>0.1671450946627271</v>
+      </c>
       <c r="G3" t="n">
-        <v>0.1671450946627271</v>
+        <v>-0.3724214950219225</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3724214950219225</v>
+        <v>0.1198883955539755</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1198883955539755</v>
-      </c>
-      <c r="J3" t="n">
         <v>-0.8857823499676581</v>
       </c>
     </row>
@@ -4357,29 +4342,24 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>SS_tonn</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SS_tonn</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F4" t="n">
+        <v>0.08988158946826497</v>
+      </c>
       <c r="G4" t="n">
-        <v>0.08988158946826497</v>
+        <v>-317.810944761693</v>
       </c>
       <c r="H4" t="n">
-        <v>-317.810944761693</v>
+        <v>42.85301614458415</v>
       </c>
       <c r="I4" t="n">
-        <v>42.85301614458415</v>
-      </c>
-      <c r="J4" t="n">
         <v>-801.1078755674507</v>
       </c>
     </row>
@@ -4401,29 +4381,24 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>TOC_tonn</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TOC_tonn</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
           <t>increasing</t>
         </is>
       </c>
+      <c r="F5" t="n">
+        <v>0.005814073275163256</v>
+      </c>
       <c r="G5" t="n">
-        <v>0.005814073275163256</v>
+        <v>32.33834151298702</v>
       </c>
       <c r="H5" t="n">
-        <v>32.33834151298702</v>
+        <v>51.24228234776216</v>
       </c>
       <c r="I5" t="n">
-        <v>51.24228234776216</v>
-      </c>
-      <c r="J5" t="n">
         <v>7.667461913262908</v>
       </c>
     </row>
@@ -4445,29 +4420,24 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Downstream. Small part of regine</t>
+          <t>TOTN_tonn</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TOTN_tonn</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F6" t="n">
+        <v>0.9015386266571279</v>
+      </c>
       <c r="G6" t="n">
-        <v>0.9015386266571279</v>
+        <v>-0.04960865528737364</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.04960865528737364</v>
+        <v>3.447309790174177</v>
       </c>
       <c r="I6" t="n">
-        <v>3.447309790174177</v>
-      </c>
-      <c r="J6" t="n">
         <v>-1.841231119921354</v>
       </c>
     </row>
@@ -4489,29 +4459,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Downstream. Small part of regine</t>
+          <t>TOTP_tonn</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TOTP_tonn</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F7" t="n">
+        <v>0.5361867719001741</v>
+      </c>
       <c r="G7" t="n">
-        <v>0.7105230229164894</v>
+        <v>0.01842394837541621</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02060588638784217</v>
+        <v>0.1450819003153632</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1450819003153632</v>
-      </c>
-      <c r="J7" t="n">
         <v>-0.1204232807037215</v>
       </c>
     </row>
@@ -4533,30 +4498,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Downstream. Small part of regine</t>
+          <t>SS_tonn</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SS_tonn</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F8" t="n">
+        <v>0.5361867719001741</v>
+      </c>
       <c r="G8" t="n">
-        <v>0.7105230229164894</v>
+        <v>14.82280902510891</v>
       </c>
       <c r="H8" t="n">
-        <v>12.57219412517942</v>
+        <v>72.57622393676469</v>
       </c>
       <c r="I8" t="n">
-        <v>72.95946966957641</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-60.17729615679767</v>
+        <v>-44.49324665217658</v>
       </c>
     </row>
     <row r="9">
@@ -4577,29 +4537,24 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Downstream. Small part of regine</t>
+          <t>TOC_tonn</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TOC_tonn</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F9" t="n">
+        <v>0.7105230229164894</v>
+      </c>
       <c r="G9" t="n">
-        <v>0.7105230229164894</v>
+        <v>5.789698885636511</v>
       </c>
       <c r="H9" t="n">
-        <v>5.789698885636511</v>
+        <v>45.94542270071138</v>
       </c>
       <c r="I9" t="n">
-        <v>45.94542270071138</v>
-      </c>
-      <c r="J9" t="n">
         <v>-28.30059170849562</v>
       </c>
     </row>
@@ -4621,29 +4576,24 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>TOTN_tonn</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TOTN_tonn</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F10" t="n">
+        <v>0.7115714636761059</v>
+      </c>
       <c r="G10" t="n">
-        <v>0.7115714636761059</v>
+        <v>0.7909426076260999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7909426076260999</v>
+        <v>4.060210804269357</v>
       </c>
       <c r="I10" t="n">
-        <v>4.060210804269357</v>
-      </c>
-      <c r="J10" t="n">
         <v>-2.513297319862212</v>
       </c>
     </row>
@@ -4665,29 +4615,24 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>TOTP_tonn</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TOTP_tonn</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F11" t="n">
+        <v>0.3417178800455669</v>
+      </c>
       <c r="G11" t="n">
-        <v>0.3417178800455669</v>
+        <v>0.1635847863991987</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1635847863991987</v>
+        <v>0.3333788183147761</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3333788183147761</v>
-      </c>
-      <c r="J11" t="n">
         <v>-0.2109114109211075</v>
       </c>
     </row>
@@ -4709,29 +4654,24 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>SS_tonn</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SS_tonn</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F12" t="n">
+        <v>0.3155727359639027</v>
+      </c>
       <c r="G12" t="n">
-        <v>0.3155727359639027</v>
+        <v>90.46210317416353</v>
       </c>
       <c r="H12" t="n">
-        <v>90.46210317416353</v>
+        <v>228.747437852305</v>
       </c>
       <c r="I12" t="n">
-        <v>228.747437852305</v>
-      </c>
-      <c r="J12" t="n">
         <v>-77.52165078066274</v>
       </c>
     </row>
@@ -4753,29 +4693,24 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>TOC_tonn</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TOC_tonn</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
           <t>increasing</t>
         </is>
       </c>
+      <c r="F13" t="n">
+        <v>0.02784675596413333</v>
+      </c>
       <c r="G13" t="n">
-        <v>0.02784675596413333</v>
+        <v>14.72111908454115</v>
       </c>
       <c r="H13" t="n">
-        <v>14.72111908454115</v>
+        <v>27.63829636658636</v>
       </c>
       <c r="I13" t="n">
-        <v>27.63829636658636</v>
-      </c>
-      <c r="J13" t="n">
         <v>3.543119269015623</v>
       </c>
     </row>
@@ -4797,29 +4732,24 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>TOTN_tonn</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TOTN_tonn</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F14" t="n">
+        <v>0.7544541774940892</v>
+      </c>
       <c r="G14" t="n">
-        <v>0.7544541774940892</v>
+        <v>-1.67258676300787</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.67258676300787</v>
+        <v>6.489809857310117</v>
       </c>
       <c r="I14" t="n">
-        <v>6.489809857310117</v>
-      </c>
-      <c r="J14" t="n">
         <v>-11.92991688483206</v>
       </c>
     </row>
@@ -4841,29 +4771,24 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>TOTP_tonn</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TOTP_tonn</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F15" t="n">
+        <v>0.7544541774940892</v>
+      </c>
       <c r="G15" t="n">
-        <v>0.7544541774940892</v>
+        <v>0.1189994454057238</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1189994454057238</v>
+        <v>0.947324519284241</v>
       </c>
       <c r="I15" t="n">
-        <v>0.947324519284241</v>
-      </c>
-      <c r="J15" t="n">
         <v>-0.3090983650786445</v>
       </c>
     </row>
@@ -4885,29 +4810,24 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>SS_tonn</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SS_tonn</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F16" t="n">
+        <v>0.2514521865080219</v>
+      </c>
       <c r="G16" t="n">
-        <v>0.2514521865080219</v>
+        <v>287.6582639425192</v>
       </c>
       <c r="H16" t="n">
-        <v>287.6582639425192</v>
+        <v>571.4515373810641</v>
       </c>
       <c r="I16" t="n">
-        <v>571.4515373810641</v>
-      </c>
-      <c r="J16" t="n">
         <v>-166.4343284814888</v>
       </c>
     </row>
@@ -4929,29 +4849,24 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>TOC_tonn</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TOC_tonn</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F17" t="n">
+        <v>0.9169652366288645</v>
+      </c>
       <c r="G17" t="n">
-        <v>0.9169652366288645</v>
+        <v>-13.19753198055915</v>
       </c>
       <c r="H17" t="n">
-        <v>-13.19753198055915</v>
+        <v>110.8271464870264</v>
       </c>
       <c r="I17" t="n">
-        <v>110.8271464870264</v>
-      </c>
-      <c r="J17" t="n">
         <v>-71.36598516787353</v>
       </c>
     </row>
@@ -4973,29 +4888,24 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>TOTN_tonn</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TOTN_tonn</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F18" t="n">
+        <v>0.9062974979468705</v>
+      </c>
       <c r="G18" t="n">
-        <v>0.9062974979468705</v>
+        <v>0.2347502116161878</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2347502116161878</v>
+        <v>3.545903393500504</v>
       </c>
       <c r="I18" t="n">
-        <v>3.545903393500504</v>
-      </c>
-      <c r="J18" t="n">
         <v>-3.746035010221934</v>
       </c>
     </row>
@@ -5017,29 +4927,24 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>TOTP_tonn</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TOTP_tonn</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F19" t="n">
+        <v>0.2894224860302206</v>
+      </c>
       <c r="G19" t="n">
-        <v>0.2894224860302206</v>
+        <v>-0.09133445919416053</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.09133445919416053</v>
+        <v>0.08512232052205072</v>
       </c>
       <c r="I19" t="n">
-        <v>0.08512232052205072</v>
-      </c>
-      <c r="J19" t="n">
         <v>-0.3149886351474135</v>
       </c>
     </row>
@@ -5061,29 +4966,24 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>SS_tonn</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SS_tonn</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F20" t="n">
+        <v>0.05704160286357429</v>
+      </c>
       <c r="G20" t="n">
-        <v>0.05704160286357429</v>
+        <v>-45.20836854787304</v>
       </c>
       <c r="H20" t="n">
-        <v>-45.20836854787304</v>
+        <v>4.97070140196347</v>
       </c>
       <c r="I20" t="n">
-        <v>4.97070140196347</v>
-      </c>
-      <c r="J20" t="n">
         <v>-95.81561464105089</v>
       </c>
     </row>
@@ -5105,29 +5005,24 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>TOC_tonn</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TOC_tonn</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
           <t>increasing</t>
         </is>
       </c>
+      <c r="F21" t="n">
+        <v>0.002858749184990295</v>
+      </c>
       <c r="G21" t="n">
-        <v>0.002858749184990295</v>
+        <v>36.37964969031034</v>
       </c>
       <c r="H21" t="n">
-        <v>36.37964969031034</v>
+        <v>53.27666810701471</v>
       </c>
       <c r="I21" t="n">
-        <v>53.27666810701471</v>
-      </c>
-      <c r="J21" t="n">
         <v>12.9874209828632</v>
       </c>
     </row>
@@ -5149,29 +5044,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>TOTN_tonn</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TOTN_tonn</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F22" t="n">
+        <v>0.8865048064138312</v>
+      </c>
       <c r="G22" t="n">
-        <v>0.8865048064138312</v>
+        <v>0.0374985130240321</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0374985130240321</v>
+        <v>0.655279015466559</v>
       </c>
       <c r="I22" t="n">
-        <v>0.655279015466559</v>
-      </c>
-      <c r="J22" t="n">
         <v>-0.5187109729654754</v>
       </c>
     </row>
@@ -5193,29 +5083,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>TOTP_tonn</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TOTP_tonn</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F23" t="n">
+        <v>0.2389927879015219</v>
+      </c>
       <c r="G23" t="n">
-        <v>0.2389927879015219</v>
+        <v>0.01792759546280634</v>
       </c>
       <c r="H23" t="n">
-        <v>0.01792759546280634</v>
+        <v>0.05175760893966993</v>
       </c>
       <c r="I23" t="n">
-        <v>0.05175760893966993</v>
-      </c>
-      <c r="J23" t="n">
         <v>-0.01233332230560929</v>
       </c>
     </row>
@@ -5237,29 +5122,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>SS_tonn</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SS_tonn</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F24" t="n">
+        <v>0.5206932698330875</v>
+      </c>
       <c r="G24" t="n">
-        <v>0.5206932698330875</v>
+        <v>4.750227955774964</v>
       </c>
       <c r="H24" t="n">
-        <v>4.750227955774964</v>
+        <v>18.06240754969724</v>
       </c>
       <c r="I24" t="n">
-        <v>18.06240754969724</v>
-      </c>
-      <c r="J24" t="n">
         <v>-9.205803072052731</v>
       </c>
     </row>
@@ -5281,29 +5161,24 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>TOC_tonn</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>TOC_tonn</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
           <t>increasing</t>
         </is>
       </c>
+      <c r="F25" t="n">
+        <v>0.004164806898991236</v>
+      </c>
       <c r="G25" t="n">
-        <v>0.004164806898991236</v>
+        <v>7.799121896608805</v>
       </c>
       <c r="H25" t="n">
-        <v>7.799121896608805</v>
+        <v>12.22626692080429</v>
       </c>
       <c r="I25" t="n">
-        <v>12.22626692080429</v>
-      </c>
-      <c r="J25" t="n">
         <v>2.632752504685588</v>
       </c>
     </row>
@@ -5325,29 +5200,24 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Downstream. Small part of regine</t>
+          <t>TOTN_tonn</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TOTN_tonn</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F26" t="n">
+        <v>0.2905607553787695</v>
+      </c>
       <c r="G26" t="n">
-        <v>0.2905607553787695</v>
+        <v>-0.174819222310143</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.174819222310143</v>
+        <v>0.1391837194768101</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1391837194768101</v>
-      </c>
-      <c r="J26" t="n">
         <v>-0.4957876948297167</v>
       </c>
     </row>
@@ -5369,29 +5239,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Downstream. Small part of regine</t>
+          <t>TOTP_tonn</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>TOTP_tonn</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F27" t="n">
+        <v>0.8215254231894769</v>
+      </c>
       <c r="G27" t="n">
-        <v>0.8215254231894769</v>
+        <v>-0.002042307879211621</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.002042307879211621</v>
+        <v>0.01464276550219087</v>
       </c>
       <c r="I27" t="n">
-        <v>0.01464276550219087</v>
-      </c>
-      <c r="J27" t="n">
         <v>-0.02242408947208864</v>
       </c>
     </row>
@@ -5413,29 +5278,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Downstream. Small part of regine</t>
+          <t>SS_tonn</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SS_tonn</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F28" t="n">
+        <v>0.8203382164336168</v>
+      </c>
       <c r="G28" t="n">
-        <v>0.8203382164336168</v>
+        <v>0.8105977526122026</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8105977526122026</v>
+        <v>10.77734451756706</v>
       </c>
       <c r="I28" t="n">
-        <v>10.77734451756706</v>
-      </c>
-      <c r="J28" t="n">
         <v>-13.34317328815222</v>
       </c>
     </row>
@@ -5457,29 +5317,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Downstream. Small part of regine</t>
+          <t>TOC_tonn</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>TOC_tonn</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
           <t>no trend</t>
         </is>
       </c>
+      <c r="F29" t="n">
+        <v>0.2241343019601669</v>
+      </c>
       <c r="G29" t="n">
-        <v>0.2241343019601669</v>
+        <v>1.090874159702638</v>
       </c>
       <c r="H29" t="n">
-        <v>1.090874159702638</v>
+        <v>3.215465606486463</v>
       </c>
       <c r="I29" t="n">
-        <v>3.215465606486463</v>
-      </c>
-      <c r="J29" t="n">
         <v>-0.7202460033019271</v>
       </c>
     </row>

--- a/data/annual_loads_waterbodies.xlsx
+++ b/data/annual_loads_waterbodies.xlsx
@@ -471,16 +471,16 @@
         <v>1995</v>
       </c>
       <c r="C2" t="n">
-        <v>43.20137400451075</v>
+        <v>51.84164880541291</v>
       </c>
       <c r="D2" t="n">
-        <v>1.261319622470048</v>
+        <v>1.513583546964058</v>
       </c>
       <c r="E2" t="n">
-        <v>430.5322911701562</v>
+        <v>516.6387494041873</v>
       </c>
       <c r="F2" t="n">
-        <v>176.8852387337406</v>
+        <v>212.2622864804887</v>
       </c>
     </row>
     <row r="3">
@@ -493,16 +493,16 @@
         <v>1996</v>
       </c>
       <c r="C3" t="n">
-        <v>42.32975369646419</v>
+        <v>50.79570443575703</v>
       </c>
       <c r="D3" t="n">
-        <v>1.085266248247397</v>
+        <v>1.302319497896878</v>
       </c>
       <c r="E3" t="n">
-        <v>384.7915608514137</v>
+        <v>461.7498730216965</v>
       </c>
       <c r="F3" t="n">
-        <v>143.6288757627007</v>
+        <v>172.3546509152409</v>
       </c>
     </row>
     <row r="4">
@@ -515,16 +515,16 @@
         <v>1997</v>
       </c>
       <c r="C4" t="n">
-        <v>30.7886815030627</v>
+        <v>36.94641780367524</v>
       </c>
       <c r="D4" t="n">
-        <v>1.162051872151194</v>
+        <v>1.394462246581433</v>
       </c>
       <c r="E4" t="n">
-        <v>428.4688124828462</v>
+        <v>514.1625749794155</v>
       </c>
       <c r="F4" t="n">
-        <v>128.6679451635399</v>
+        <v>154.4015341962478</v>
       </c>
     </row>
     <row r="5">
@@ -537,16 +537,16 @@
         <v>1998</v>
       </c>
       <c r="C5" t="n">
-        <v>36.94448436197132</v>
+        <v>44.33338123436558</v>
       </c>
       <c r="D5" t="n">
-        <v>1.682400057017694</v>
+        <v>2.018880068421233</v>
       </c>
       <c r="E5" t="n">
-        <v>637.1842858735313</v>
+        <v>764.6211430482372</v>
       </c>
       <c r="F5" t="n">
-        <v>175.9291755540946</v>
+        <v>211.1150106649136</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         <v>1999</v>
       </c>
       <c r="C6" t="n">
-        <v>60.88915283023869</v>
+        <v>73.0669833962864</v>
       </c>
       <c r="D6" t="n">
-        <v>3.273467950963915</v>
+        <v>3.928161541156698</v>
       </c>
       <c r="E6" t="n">
-        <v>1481.66301410922</v>
+        <v>1777.995616931064</v>
       </c>
       <c r="F6" t="n">
-        <v>332.185908457374</v>
+        <v>398.6230901488487</v>
       </c>
     </row>
     <row r="7">
@@ -581,16 +581,16 @@
         <v>2000</v>
       </c>
       <c r="C7" t="n">
-        <v>63.48058038141561</v>
+        <v>76.17669645769872</v>
       </c>
       <c r="D7" t="n">
-        <v>3.812702042892715</v>
+        <v>4.575242451471255</v>
       </c>
       <c r="E7" t="n">
-        <v>1151.415594585329</v>
+        <v>1381.698713502394</v>
       </c>
       <c r="F7" t="n">
-        <v>428.7557406319572</v>
+        <v>514.5068887583486</v>
       </c>
     </row>
     <row r="8">
@@ -603,16 +603,16 @@
         <v>2001</v>
       </c>
       <c r="C8" t="n">
-        <v>43.83372228170499</v>
+        <v>52.60046673804597</v>
       </c>
       <c r="D8" t="n">
-        <v>1.566493047153545</v>
+        <v>1.879791656584253</v>
       </c>
       <c r="E8" t="n">
-        <v>344.6645518909453</v>
+        <v>413.5974622691346</v>
       </c>
       <c r="F8" t="n">
-        <v>224.7171589006246</v>
+        <v>269.6605906807495</v>
       </c>
     </row>
     <row r="9">
@@ -625,16 +625,16 @@
         <v>2002</v>
       </c>
       <c r="C9" t="n">
-        <v>39.15298310684493</v>
+        <v>46.98357972821391</v>
       </c>
       <c r="D9" t="n">
-        <v>1.296743224244016</v>
+        <v>1.55609186909282</v>
       </c>
       <c r="E9" t="n">
-        <v>289.0914156518298</v>
+        <v>346.9096987821957</v>
       </c>
       <c r="F9" t="n">
-        <v>195.8159412158462</v>
+        <v>234.9791294590155</v>
       </c>
     </row>
     <row r="10">
@@ -647,16 +647,16 @@
         <v>2003</v>
       </c>
       <c r="C10" t="n">
-        <v>59.26498380326215</v>
+        <v>71.11798056391461</v>
       </c>
       <c r="D10" t="n">
-        <v>1.496223700735488</v>
+        <v>1.795468440882586</v>
       </c>
       <c r="E10" t="n">
-        <v>236.623580022185</v>
+        <v>283.9482960266221</v>
       </c>
       <c r="F10" t="n">
-        <v>187.050520337289</v>
+        <v>224.4606244047468</v>
       </c>
     </row>
     <row r="11">
@@ -669,16 +669,16 @@
         <v>2004</v>
       </c>
       <c r="C11" t="n">
-        <v>40.28778276183817</v>
+        <v>48.3453393142058</v>
       </c>
       <c r="D11" t="n">
-        <v>1.173397412360143</v>
+        <v>1.408076894832172</v>
       </c>
       <c r="E11" t="n">
-        <v>175.0898537937713</v>
+        <v>210.1078245525255</v>
       </c>
       <c r="F11" t="n">
-        <v>178.6440552342183</v>
+        <v>214.3728662810618</v>
       </c>
     </row>
     <row r="12">
@@ -691,16 +691,16 @@
         <v>2005</v>
       </c>
       <c r="C12" t="n">
-        <v>35.27460842320991</v>
+        <v>42.32953010785189</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9076335690840078</v>
+        <v>1.08916028290081</v>
       </c>
       <c r="E12" t="n">
-        <v>202.5992098643331</v>
+        <v>243.1190518371997</v>
       </c>
       <c r="F12" t="n">
-        <v>168.09112907935</v>
+        <v>201.7093548952199</v>
       </c>
     </row>
     <row r="13">
@@ -713,16 +713,16 @@
         <v>2006</v>
       </c>
       <c r="C13" t="n">
-        <v>71.11943060173105</v>
+        <v>85.34331672207726</v>
       </c>
       <c r="D13" t="n">
-        <v>2.310973165067154</v>
+        <v>2.773167798080584</v>
       </c>
       <c r="E13" t="n">
-        <v>563.5378612971094</v>
+        <v>676.2454335565311</v>
       </c>
       <c r="F13" t="n">
-        <v>315.0965301846499</v>
+        <v>378.1158362215797</v>
       </c>
     </row>
     <row r="14">
@@ -735,16 +735,16 @@
         <v>2007</v>
       </c>
       <c r="C14" t="n">
-        <v>42.525725321428</v>
+        <v>51.03087038571355</v>
       </c>
       <c r="D14" t="n">
-        <v>1.925476594795005</v>
+        <v>2.310571913754004</v>
       </c>
       <c r="E14" t="n">
-        <v>529.4723937237975</v>
+        <v>635.3668724685566</v>
       </c>
       <c r="F14" t="n">
-        <v>192.6121906718114</v>
+        <v>231.1346288061736</v>
       </c>
     </row>
     <row r="15">
@@ -757,16 +757,16 @@
         <v>2008</v>
       </c>
       <c r="C15" t="n">
-        <v>55.62221865210576</v>
+        <v>66.74666238252688</v>
       </c>
       <c r="D15" t="n">
-        <v>2.551412911162748</v>
+        <v>3.061695493395296</v>
       </c>
       <c r="E15" t="n">
-        <v>705.3932270129316</v>
+        <v>846.471872415518</v>
       </c>
       <c r="F15" t="n">
-        <v>321.9162259926705</v>
+        <v>386.2994711912046</v>
       </c>
     </row>
     <row r="16">
@@ -779,13 +779,13 @@
         <v>2009</v>
       </c>
       <c r="C16" t="n">
-        <v>31.23866365935109</v>
+        <v>37.48639639122129</v>
       </c>
       <c r="D16" t="n">
-        <v>1.087661960440927</v>
+        <v>1.305194352529113</v>
       </c>
       <c r="E16" t="n">
-        <v>285.6603121850598</v>
+        <v>342.7923746220715</v>
       </c>
       <c r="F16" t="inlineStr"/>
     </row>
@@ -799,16 +799,16 @@
         <v>2010</v>
       </c>
       <c r="C17" t="n">
-        <v>40.71766627027407</v>
+        <v>48.86119952432888</v>
       </c>
       <c r="D17" t="n">
-        <v>1.599326527037739</v>
+        <v>1.919191832445285</v>
       </c>
       <c r="E17" t="n">
-        <v>500.6418738911458</v>
+        <v>600.7702486693747</v>
       </c>
       <c r="F17" t="n">
-        <v>168.6949906927315</v>
+        <v>202.4339888312778</v>
       </c>
     </row>
     <row r="18">
@@ -821,16 +821,16 @@
         <v>2011</v>
       </c>
       <c r="C18" t="n">
-        <v>54.35411525693454</v>
+        <v>65.22493830832144</v>
       </c>
       <c r="D18" t="n">
-        <v>2.827173941744334</v>
+        <v>3.3926087300932</v>
       </c>
       <c r="E18" t="n">
-        <v>1061.313848199848</v>
+        <v>1273.576617839817</v>
       </c>
       <c r="F18" t="n">
-        <v>308.1332520069056</v>
+        <v>369.7599024082867</v>
       </c>
     </row>
     <row r="19">
@@ -843,16 +843,16 @@
         <v>2012</v>
       </c>
       <c r="C19" t="n">
-        <v>48.10954907580363</v>
+        <v>57.73145889096433</v>
       </c>
       <c r="D19" t="n">
-        <v>2.489000152481097</v>
+        <v>2.986800182977315</v>
       </c>
       <c r="E19" t="n">
-        <v>854.3065472859237</v>
+        <v>1025.167856743108</v>
       </c>
       <c r="F19" t="n">
-        <v>284.2200128459098</v>
+        <v>341.0640154150917</v>
       </c>
     </row>
     <row r="20">
@@ -865,16 +865,16 @@
         <v>2013</v>
       </c>
       <c r="C20" t="n">
-        <v>51.73020766964065</v>
+        <v>62.07624920356877</v>
       </c>
       <c r="D20" t="n">
-        <v>3.097890690352663</v>
+        <v>3.717468828423194</v>
       </c>
       <c r="E20" t="n">
-        <v>964.2033419518884</v>
+        <v>1157.044010342265</v>
       </c>
       <c r="F20" t="n">
-        <v>292.9160040032267</v>
+        <v>351.499204803872</v>
       </c>
     </row>
     <row r="21">
@@ -887,13 +887,13 @@
         <v>2014</v>
       </c>
       <c r="C21" t="n">
-        <v>46.441473918414</v>
+        <v>55.72976870209679</v>
       </c>
       <c r="D21" t="n">
-        <v>1.992350996243776</v>
+        <v>2.390821195492531</v>
       </c>
       <c r="E21" t="n">
-        <v>667.6330104441525</v>
+        <v>801.1596125329828</v>
       </c>
       <c r="F21" t="inlineStr"/>
     </row>
@@ -907,16 +907,16 @@
         <v>2015</v>
       </c>
       <c r="C22" t="n">
-        <v>50.12157652915691</v>
+        <v>60.14589183498828</v>
       </c>
       <c r="D22" t="n">
-        <v>1.987567098013817</v>
+        <v>2.385080517616581</v>
       </c>
       <c r="E22" t="n">
-        <v>557.2573241264574</v>
+        <v>668.7087889517487</v>
       </c>
       <c r="F22" t="n">
-        <v>341.5325004581801</v>
+        <v>409.839000549816</v>
       </c>
     </row>
     <row r="23">
@@ -929,16 +929,16 @@
         <v>2016</v>
       </c>
       <c r="C23" t="n">
-        <v>34.81500936149426</v>
+        <v>41.77801123379311</v>
       </c>
       <c r="D23" t="n">
-        <v>1.729282441751971</v>
+        <v>2.075138930102365</v>
       </c>
       <c r="E23" t="n">
-        <v>890.333513571689</v>
+        <v>1068.400216286027</v>
       </c>
       <c r="F23" t="n">
-        <v>264.2084464709084</v>
+        <v>317.05013576509</v>
       </c>
     </row>
     <row r="24">
@@ -951,13 +951,13 @@
         <v>2017</v>
       </c>
       <c r="C24" t="n">
-        <v>36.64942008675934</v>
+        <v>43.97930410411122</v>
       </c>
       <c r="D24" t="n">
-        <v>1.51916813305297</v>
+        <v>1.823001759663564</v>
       </c>
       <c r="E24" t="n">
-        <v>409.91303210264</v>
+        <v>491.8956385231678</v>
       </c>
       <c r="F24" t="inlineStr"/>
     </row>
@@ -971,13 +971,13 @@
         <v>2018</v>
       </c>
       <c r="C25" t="n">
-        <v>54.06501140348414</v>
+        <v>64.87801368418097</v>
       </c>
       <c r="D25" t="n">
-        <v>1.553480440897957</v>
+        <v>1.864176529077547</v>
       </c>
       <c r="E25" t="n">
-        <v>462.2278424899659</v>
+        <v>554.6734109879592</v>
       </c>
       <c r="F25" t="inlineStr"/>
     </row>
@@ -991,16 +991,16 @@
         <v>2019</v>
       </c>
       <c r="C26" t="n">
-        <v>69.10179710979064</v>
+        <v>82.92215653174877</v>
       </c>
       <c r="D26" t="n">
-        <v>2.713216904142537</v>
+        <v>3.255860284971044</v>
       </c>
       <c r="E26" t="n">
-        <v>873.945494551067</v>
+        <v>1048.734593461281</v>
       </c>
       <c r="F26" t="n">
-        <v>437.0628405198718</v>
+        <v>524.4754086238461</v>
       </c>
     </row>
     <row r="27">
@@ -1013,16 +1013,16 @@
         <v>2020</v>
       </c>
       <c r="C27" t="n">
-        <v>59.58334939117473</v>
+        <v>71.50001926940968</v>
       </c>
       <c r="D27" t="n">
-        <v>3.153778870476885</v>
+        <v>3.784534644572263</v>
       </c>
       <c r="E27" t="n">
-        <v>1113.886007673586</v>
+        <v>1336.663209208303</v>
       </c>
       <c r="F27" t="n">
-        <v>482.5419117538477</v>
+        <v>579.0502941046175</v>
       </c>
     </row>
     <row r="28">
@@ -1035,16 +1035,16 @@
         <v>2021</v>
       </c>
       <c r="C28" t="n">
-        <v>34.30228583477979</v>
+        <v>41.16274300173575</v>
       </c>
       <c r="D28" t="n">
-        <v>1.398733643988681</v>
+        <v>1.678480372786416</v>
       </c>
       <c r="E28" t="n">
-        <v>482.1507821386244</v>
+        <v>578.5809385663491</v>
       </c>
       <c r="F28" t="n">
-        <v>264.0350349961961</v>
+        <v>316.8420419954354</v>
       </c>
     </row>
     <row r="29">
@@ -1057,16 +1057,16 @@
         <v>2022</v>
       </c>
       <c r="C29" t="n">
-        <v>29.73964560330344</v>
+        <v>35.68757472396414</v>
       </c>
       <c r="D29" t="n">
-        <v>1.156264865953755</v>
+        <v>1.387517839144506</v>
       </c>
       <c r="E29" t="n">
-        <v>269.3917339169381</v>
+        <v>323.2700807003258</v>
       </c>
       <c r="F29" t="n">
-        <v>203.9761139203364</v>
+        <v>244.7713367044038</v>
       </c>
     </row>
     <row r="30">
@@ -1079,16 +1079,16 @@
         <v>2023</v>
       </c>
       <c r="C30" t="n">
-        <v>55.89332021761633</v>
+        <v>67.07198426113959</v>
       </c>
       <c r="D30" t="n">
-        <v>3.018291752865367</v>
+        <v>3.621950103438442</v>
       </c>
       <c r="E30" t="n">
-        <v>644.2917365452838</v>
+        <v>773.1500838543401</v>
       </c>
       <c r="F30" t="n">
-        <v>593.9176318773455</v>
+        <v>712.7011582528146</v>
       </c>
     </row>
     <row r="31">
@@ -1101,16 +1101,16 @@
         <v>2024</v>
       </c>
       <c r="C31" t="n">
-        <v>43.48422373890934</v>
+        <v>52.1810684866912</v>
       </c>
       <c r="D31" t="n">
-        <v>1.662821006579109</v>
+        <v>1.995385207894931</v>
       </c>
       <c r="E31" t="n">
-        <v>411.2272582713248</v>
+        <v>493.4727099255898</v>
       </c>
       <c r="F31" t="n">
-        <v>427.0880139833978</v>
+        <v>512.5056167800774</v>
       </c>
     </row>
     <row r="32">
@@ -1123,10 +1123,10 @@
         <v>1980</v>
       </c>
       <c r="C32" t="n">
-        <v>394.9792023168154</v>
+        <v>473.9750427801786</v>
       </c>
       <c r="D32" t="n">
-        <v>17.78827877368291</v>
+        <v>21.3459345284195</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
@@ -1141,16 +1141,16 @@
         <v>1981</v>
       </c>
       <c r="C33" t="n">
-        <v>376.8331787531924</v>
+        <v>452.1998145038306</v>
       </c>
       <c r="D33" t="n">
-        <v>27.63547584305347</v>
+        <v>33.16257101166416</v>
       </c>
       <c r="E33" t="n">
-        <v>4693.772018170561</v>
+        <v>5632.526421804672</v>
       </c>
       <c r="F33" t="n">
-        <v>1018.956404069343</v>
+        <v>1222.747684883211</v>
       </c>
     </row>
     <row r="34">
@@ -1163,16 +1163,16 @@
         <v>1982</v>
       </c>
       <c r="C34" t="n">
-        <v>273.6058978853924</v>
+        <v>328.3270774624711</v>
       </c>
       <c r="D34" t="n">
-        <v>18.57949684568227</v>
+        <v>22.29539621481872</v>
       </c>
       <c r="E34" t="n">
-        <v>5066.679231237249</v>
+        <v>6080.015077484698</v>
       </c>
       <c r="F34" t="n">
-        <v>1223.942126596877</v>
+        <v>1468.730551916253</v>
       </c>
     </row>
     <row r="35">
@@ -1185,13 +1185,13 @@
         <v>1983</v>
       </c>
       <c r="C35" t="n">
-        <v>541.5424996070044</v>
+        <v>649.8509995284052</v>
       </c>
       <c r="D35" t="n">
-        <v>33.78322516601764</v>
+        <v>40.53987019922116</v>
       </c>
       <c r="E35" t="n">
-        <v>3865.31631873066</v>
+        <v>4638.379582476791</v>
       </c>
       <c r="F35" t="inlineStr"/>
     </row>
@@ -1205,14 +1205,14 @@
         <v>1987</v>
       </c>
       <c r="C36" t="n">
-        <v>563.8970280438901</v>
+        <v>676.6764336526682</v>
       </c>
       <c r="D36" t="n">
-        <v>72.35174638140985</v>
+        <v>86.82209565769185</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
-        <v>1750.202039942195</v>
+        <v>2100.242447930635</v>
       </c>
     </row>
     <row r="37">
@@ -1225,16 +1225,16 @@
         <v>1988</v>
       </c>
       <c r="C37" t="n">
-        <v>339.0315963613396</v>
+        <v>406.8379156336074</v>
       </c>
       <c r="D37" t="n">
-        <v>5.386361821333769</v>
+        <v>6.463634185600521</v>
       </c>
       <c r="E37" t="n">
-        <v>4495.633270406929</v>
+        <v>5394.759924488313</v>
       </c>
       <c r="F37" t="n">
-        <v>1630.292009142133</v>
+        <v>1956.35041097056</v>
       </c>
     </row>
     <row r="38">
@@ -1247,16 +1247,16 @@
         <v>1989</v>
       </c>
       <c r="C38" t="n">
-        <v>426.0975791298213</v>
+        <v>511.3170949557855</v>
       </c>
       <c r="D38" t="n">
-        <v>10.53272649032989</v>
+        <v>12.63927178839586</v>
       </c>
       <c r="E38" t="n">
-        <v>3522.234196135858</v>
+        <v>4226.681035363031</v>
       </c>
       <c r="F38" t="n">
-        <v>870.7474044887106</v>
+        <v>1044.896885386453</v>
       </c>
     </row>
     <row r="39">
@@ -1269,16 +1269,16 @@
         <v>1990</v>
       </c>
       <c r="C39" t="n">
-        <v>541.6002014412019</v>
+        <v>649.9202417294422</v>
       </c>
       <c r="D39" t="n">
-        <v>14.64782241705421</v>
+        <v>17.57738690046505</v>
       </c>
       <c r="E39" t="n">
-        <v>6845.790629637511</v>
+        <v>8214.948755565014</v>
       </c>
       <c r="F39" t="n">
-        <v>816.4350230676083</v>
+        <v>979.7220276811303</v>
       </c>
     </row>
     <row r="40">
@@ -1291,13 +1291,13 @@
         <v>1991</v>
       </c>
       <c r="C40" t="n">
-        <v>648.9387693665694</v>
+        <v>778.7265232398832</v>
       </c>
       <c r="D40" t="n">
-        <v>8.653368815762475</v>
+        <v>10.38404257891497</v>
       </c>
       <c r="E40" t="n">
-        <v>3826.573811432509</v>
+        <v>4591.88857371901</v>
       </c>
       <c r="F40" t="inlineStr"/>
     </row>
@@ -1311,16 +1311,16 @@
         <v>1992</v>
       </c>
       <c r="C41" t="n">
-        <v>309.0649318203975</v>
+        <v>370.8779181844769</v>
       </c>
       <c r="D41" t="n">
-        <v>5.289589561498899</v>
+        <v>6.347507473798679</v>
       </c>
       <c r="E41" t="n">
-        <v>2077.809166428574</v>
+        <v>2493.370999714289</v>
       </c>
       <c r="F41" t="n">
-        <v>782.2311620668191</v>
+        <v>938.677394480183</v>
       </c>
     </row>
     <row r="42">
@@ -1333,16 +1333,16 @@
         <v>1993</v>
       </c>
       <c r="C42" t="n">
-        <v>394.0646926976543</v>
+        <v>472.877631237185</v>
       </c>
       <c r="D42" t="n">
-        <v>9.658741160238577</v>
+        <v>11.59048939228629</v>
       </c>
       <c r="E42" t="n">
-        <v>3349.603817425647</v>
+        <v>4019.524580910777</v>
       </c>
       <c r="F42" t="n">
-        <v>1139.473644292246</v>
+        <v>1367.368373150696</v>
       </c>
     </row>
     <row r="43">
@@ -1355,16 +1355,16 @@
         <v>1994</v>
       </c>
       <c r="C43" t="n">
-        <v>904.3804227978051</v>
+        <v>1085.256507357366</v>
       </c>
       <c r="D43" t="n">
-        <v>14.95606301422918</v>
+        <v>17.94727561707502</v>
       </c>
       <c r="E43" t="n">
-        <v>2338.593141988471</v>
+        <v>2806.311770386166</v>
       </c>
       <c r="F43" t="n">
-        <v>1690.546202937837</v>
+        <v>2028.655443525404</v>
       </c>
     </row>
     <row r="44">
@@ -1377,16 +1377,16 @@
         <v>1995</v>
       </c>
       <c r="C44" t="n">
-        <v>424.7959703640047</v>
+        <v>509.7551644368058</v>
       </c>
       <c r="D44" t="n">
-        <v>7.980193844527869</v>
+        <v>9.576232613433445</v>
       </c>
       <c r="E44" t="n">
-        <v>2687.544978577406</v>
+        <v>3225.053974292888</v>
       </c>
       <c r="F44" t="n">
-        <v>1026.701703299279</v>
+        <v>1232.042043959136</v>
       </c>
     </row>
     <row r="45">
@@ -1399,16 +1399,16 @@
         <v>1996</v>
       </c>
       <c r="C45" t="n">
-        <v>416.1330797102987</v>
+        <v>499.3596956523585</v>
       </c>
       <c r="D45" t="n">
-        <v>5.830070125185403</v>
+        <v>6.996084150222485</v>
       </c>
       <c r="E45" t="n">
-        <v>1917.358823858252</v>
+        <v>2300.830588629901</v>
       </c>
       <c r="F45" t="n">
-        <v>679.5771462426197</v>
+        <v>815.4925754911436</v>
       </c>
     </row>
     <row r="46">
@@ -1421,16 +1421,16 @@
         <v>1997</v>
       </c>
       <c r="C46" t="n">
-        <v>599.8942257478554</v>
+        <v>719.8730708974265</v>
       </c>
       <c r="D46" t="n">
-        <v>10.77716241750968</v>
+        <v>12.93259490101161</v>
       </c>
       <c r="E46" t="n">
-        <v>3500.279859886025</v>
+        <v>4200.335831863231</v>
       </c>
       <c r="F46" t="n">
-        <v>852.0365592095708</v>
+        <v>1022.443871051485</v>
       </c>
     </row>
     <row r="47">
@@ -1443,16 +1443,16 @@
         <v>1998</v>
       </c>
       <c r="C47" t="n">
-        <v>532.2285694314418</v>
+        <v>638.6742833177299</v>
       </c>
       <c r="D47" t="n">
-        <v>14.82866276135766</v>
+        <v>17.79439531362919</v>
       </c>
       <c r="E47" t="n">
-        <v>4048.211810206681</v>
+        <v>4857.854172248018</v>
       </c>
       <c r="F47" t="n">
-        <v>1100.252283111433</v>
+        <v>1320.302739733719</v>
       </c>
     </row>
     <row r="48">
@@ -1465,16 +1465,16 @@
         <v>1999</v>
       </c>
       <c r="C48" t="n">
-        <v>519.2964044596686</v>
+        <v>623.1556853516021</v>
       </c>
       <c r="D48" t="n">
-        <v>14.08972873674516</v>
+        <v>16.90767448409418</v>
       </c>
       <c r="E48" t="n">
-        <v>5899.771955106919</v>
+        <v>7079.726346128299</v>
       </c>
       <c r="F48" t="n">
-        <v>1773.153639953628</v>
+        <v>2127.784367944353</v>
       </c>
     </row>
     <row r="49">
@@ -1487,16 +1487,16 @@
         <v>2000</v>
       </c>
       <c r="C49" t="n">
-        <v>683.9029780109624</v>
+        <v>820.6835736131554</v>
       </c>
       <c r="D49" t="n">
-        <v>31.02789760020594</v>
+        <v>37.23347712024713</v>
       </c>
       <c r="E49" t="n">
-        <v>10552.4912941688</v>
+        <v>12662.98955300256</v>
       </c>
       <c r="F49" t="n">
-        <v>2577.86217876022</v>
+        <v>3093.434614512265</v>
       </c>
     </row>
     <row r="50">
@@ -1509,16 +1509,16 @@
         <v>2001</v>
       </c>
       <c r="C50" t="n">
-        <v>553.8803714997437</v>
+        <v>664.6564457996925</v>
       </c>
       <c r="D50" t="n">
-        <v>21.28140709500083</v>
+        <v>25.53768851400098</v>
       </c>
       <c r="E50" t="n">
-        <v>4232.592612825022</v>
+        <v>5079.111135390028</v>
       </c>
       <c r="F50" t="n">
-        <v>1477.498966917441</v>
+        <v>1772.998760300929</v>
       </c>
     </row>
     <row r="51">
@@ -1531,16 +1531,16 @@
         <v>2002</v>
       </c>
       <c r="C51" t="n">
-        <v>714.7686737995298</v>
+        <v>857.7224085594355</v>
       </c>
       <c r="D51" t="n">
-        <v>8.61870250809555</v>
+        <v>10.34244300971466</v>
       </c>
       <c r="E51" t="n">
-        <v>2193.886788120488</v>
+        <v>2632.664145744585</v>
       </c>
       <c r="F51" t="n">
-        <v>1257.888931541018</v>
+        <v>1509.466717849222</v>
       </c>
     </row>
     <row r="52">
@@ -1553,16 +1553,16 @@
         <v>2003</v>
       </c>
       <c r="C52" t="n">
-        <v>609.6024253004979</v>
+        <v>731.5229103605973</v>
       </c>
       <c r="D52" t="n">
-        <v>4.378660750720065</v>
+        <v>5.254392900864078</v>
       </c>
       <c r="E52" t="n">
-        <v>1614.894792833506</v>
+        <v>1937.873751400207</v>
       </c>
       <c r="F52" t="n">
-        <v>909.1871985017123</v>
+        <v>1091.024638202054</v>
       </c>
     </row>
     <row r="53">
@@ -1575,16 +1575,16 @@
         <v>2004</v>
       </c>
       <c r="C53" t="n">
-        <v>402.3758715733695</v>
+        <v>482.8510458880432</v>
       </c>
       <c r="D53" t="n">
-        <v>7.903264168385567</v>
+        <v>9.483917002062677</v>
       </c>
       <c r="E53" t="n">
-        <v>1278.224729610259</v>
+        <v>1533.86967553231</v>
       </c>
       <c r="F53" t="n">
-        <v>1106.173876658406</v>
+        <v>1327.408651990087</v>
       </c>
     </row>
     <row r="54">
@@ -1597,16 +1597,16 @@
         <v>2005</v>
       </c>
       <c r="C54" t="n">
-        <v>276.2557678084816</v>
+        <v>331.5069213701777</v>
       </c>
       <c r="D54" t="n">
-        <v>5.16941249090159</v>
+        <v>6.203294989081905</v>
       </c>
       <c r="E54" t="n">
-        <v>999.8011856516082</v>
+        <v>1199.76142278193</v>
       </c>
       <c r="F54" t="n">
-        <v>882.4642945912068</v>
+        <v>1058.957153509448</v>
       </c>
     </row>
     <row r="55">
@@ -1619,16 +1619,16 @@
         <v>2006</v>
       </c>
       <c r="C55" t="n">
-        <v>383.4789652561967</v>
+        <v>460.1747583074363</v>
       </c>
       <c r="D55" t="n">
-        <v>9.701619469353291</v>
+        <v>11.64194336322395</v>
       </c>
       <c r="E55" t="n">
-        <v>2379.684409484527</v>
+        <v>2855.621291381434</v>
       </c>
       <c r="F55" t="n">
-        <v>1533.75219058068</v>
+        <v>1840.502628696817</v>
       </c>
     </row>
     <row r="56">
@@ -1641,16 +1641,16 @@
         <v>2008</v>
       </c>
       <c r="C56" t="n">
-        <v>407.264051760721</v>
+        <v>488.7168621128653</v>
       </c>
       <c r="D56" t="n">
-        <v>13.27872332957156</v>
+        <v>15.93446799548587</v>
       </c>
       <c r="E56" t="n">
-        <v>3042.996397054112</v>
+        <v>3651.595676464933</v>
       </c>
       <c r="F56" t="n">
-        <v>1626.643946712841</v>
+        <v>1951.972736055409</v>
       </c>
     </row>
     <row r="57">
@@ -1663,13 +1663,13 @@
         <v>2010</v>
       </c>
       <c r="C57" t="n">
-        <v>215.3845212393887</v>
+        <v>258.4614254872664</v>
       </c>
       <c r="D57" t="n">
-        <v>6.33999231091919</v>
+        <v>7.607990773103028</v>
       </c>
       <c r="E57" t="n">
-        <v>840.8905494972206</v>
+        <v>1009.068659396665</v>
       </c>
       <c r="F57" t="inlineStr"/>
     </row>
@@ -1683,16 +1683,16 @@
         <v>2011</v>
       </c>
       <c r="C58" t="n">
-        <v>304.0878119798049</v>
+        <v>364.905374375766</v>
       </c>
       <c r="D58" t="n">
-        <v>9.519110496303586</v>
+        <v>11.42293259556431</v>
       </c>
       <c r="E58" t="n">
-        <v>1649.45706677408</v>
+        <v>1979.348480128897</v>
       </c>
       <c r="F58" t="n">
-        <v>1609.9651963633</v>
+        <v>1931.958235635961</v>
       </c>
     </row>
     <row r="59">
@@ -1705,16 +1705,16 @@
         <v>2012</v>
       </c>
       <c r="C59" t="n">
-        <v>399.0934625316593</v>
+        <v>478.9121550379911</v>
       </c>
       <c r="D59" t="n">
-        <v>10.93957613984765</v>
+        <v>13.12749136781718</v>
       </c>
       <c r="E59" t="n">
-        <v>2924.810095213497</v>
+        <v>3509.772114256197</v>
       </c>
       <c r="F59" t="n">
-        <v>1516.322721238507</v>
+        <v>1819.587265486208</v>
       </c>
     </row>
     <row r="60">
@@ -1727,13 +1727,13 @@
         <v>2013</v>
       </c>
       <c r="C60" t="n">
-        <v>315.2722043676792</v>
+        <v>378.3266452412149</v>
       </c>
       <c r="D60" t="n">
-        <v>8.439221473803467</v>
+        <v>10.12706576856416</v>
       </c>
       <c r="E60" t="n">
-        <v>1696.594734093885</v>
+        <v>2035.913680912662</v>
       </c>
       <c r="F60" t="inlineStr"/>
     </row>
@@ -1747,16 +1747,16 @@
         <v>2015</v>
       </c>
       <c r="C61" t="n">
-        <v>424.3431395410091</v>
+        <v>509.2117674492108</v>
       </c>
       <c r="D61" t="n">
-        <v>6.713034036946975</v>
+        <v>8.05564084433637</v>
       </c>
       <c r="E61" t="n">
-        <v>1125.186238887552</v>
+        <v>1350.223486665062</v>
       </c>
       <c r="F61" t="n">
-        <v>1864.454927503133</v>
+        <v>2237.34591300376</v>
       </c>
     </row>
     <row r="62">
@@ -1769,13 +1769,13 @@
         <v>2016</v>
       </c>
       <c r="C62" t="n">
-        <v>375.0282227875504</v>
+        <v>450.0338673450603</v>
       </c>
       <c r="D62" t="n">
-        <v>9.15886732870422</v>
+        <v>10.99064079444506</v>
       </c>
       <c r="E62" t="n">
-        <v>2879.384534703782</v>
+        <v>3455.261441644539</v>
       </c>
       <c r="F62" t="inlineStr"/>
     </row>
@@ -1789,13 +1789,13 @@
         <v>2017</v>
       </c>
       <c r="C63" t="n">
-        <v>344.9716178358077</v>
+        <v>413.9659414029693</v>
       </c>
       <c r="D63" t="n">
-        <v>5.943935301964698</v>
+        <v>7.132722362357639</v>
       </c>
       <c r="E63" t="n">
-        <v>1232.088196099771</v>
+        <v>1478.505835319725</v>
       </c>
       <c r="F63" t="inlineStr"/>
     </row>
@@ -1809,13 +1809,13 @@
         <v>2018</v>
       </c>
       <c r="C64" t="n">
-        <v>447.7699427270102</v>
+        <v>537.3239312724121</v>
       </c>
       <c r="D64" t="n">
-        <v>7.502769895072218</v>
+        <v>9.003323874086661</v>
       </c>
       <c r="E64" t="n">
-        <v>1798.744051736745</v>
+        <v>2158.492862084094</v>
       </c>
       <c r="F64" t="inlineStr"/>
     </row>
@@ -1829,16 +1829,16 @@
         <v>2019</v>
       </c>
       <c r="C65" t="n">
-        <v>629.7823196774591</v>
+        <v>755.7387836129509</v>
       </c>
       <c r="D65" t="n">
-        <v>12.71257741765722</v>
+        <v>15.25509290118866</v>
       </c>
       <c r="E65" t="n">
-        <v>3265.009111140644</v>
+        <v>3918.010933368773</v>
       </c>
       <c r="F65" t="n">
-        <v>2220.701200956216</v>
+        <v>2664.84144114746</v>
       </c>
     </row>
     <row r="66">
@@ -1851,16 +1851,16 @@
         <v>2020</v>
       </c>
       <c r="C66" t="n">
-        <v>686.4575441115153</v>
+        <v>823.7490529338186</v>
       </c>
       <c r="D66" t="n">
-        <v>35.24653428054845</v>
+        <v>42.29584113665814</v>
       </c>
       <c r="E66" t="n">
-        <v>8636.179001347778</v>
+        <v>10363.41480161733</v>
       </c>
       <c r="F66" t="n">
-        <v>3260.365598806924</v>
+        <v>3912.438718568309</v>
       </c>
     </row>
     <row r="67">
@@ -1873,16 +1873,16 @@
         <v>2023</v>
       </c>
       <c r="C67" t="n">
-        <v>451.6564502719066</v>
+        <v>541.9877403262878</v>
       </c>
       <c r="D67" t="n">
-        <v>20.90263497192434</v>
+        <v>25.08316196630921</v>
       </c>
       <c r="E67" t="n">
-        <v>7121.223306206118</v>
+        <v>8545.467967447337</v>
       </c>
       <c r="F67" t="n">
-        <v>3241.310869317224</v>
+        <v>3889.573043180668</v>
       </c>
     </row>
     <row r="68">
@@ -1895,16 +1895,16 @@
         <v>2024</v>
       </c>
       <c r="C68" t="n">
-        <v>451.5095891155092</v>
+        <v>541.811506938611</v>
       </c>
       <c r="D68" t="n">
-        <v>19.87865706207046</v>
+        <v>23.85438847448456</v>
       </c>
       <c r="E68" t="n">
-        <v>3696.20874520458</v>
+        <v>4435.450494245495</v>
       </c>
       <c r="F68" t="n">
-        <v>2945.222627237377</v>
+        <v>3534.267152684851</v>
       </c>
     </row>
     <row r="69">
@@ -1917,13 +1917,13 @@
         <v>1981</v>
       </c>
       <c r="C69" t="n">
-        <v>315.1324929067821</v>
+        <v>378.1589914881386</v>
       </c>
       <c r="D69" t="n">
-        <v>57.15804645704986</v>
+        <v>68.58965574845983</v>
       </c>
       <c r="E69" t="n">
-        <v>33404.57625230787</v>
+        <v>40085.49150276944</v>
       </c>
       <c r="F69" t="inlineStr"/>
     </row>
@@ -1937,13 +1937,13 @@
         <v>1982</v>
       </c>
       <c r="C70" t="n">
-        <v>415.3668310721181</v>
+        <v>498.4401972865416</v>
       </c>
       <c r="D70" t="n">
-        <v>63.9849757832741</v>
+        <v>76.78197093992893</v>
       </c>
       <c r="E70" t="n">
-        <v>56147.4241046187</v>
+        <v>67376.9089255424</v>
       </c>
       <c r="F70" t="inlineStr"/>
     </row>
@@ -1957,16 +1957,16 @@
         <v>1983</v>
       </c>
       <c r="C71" t="n">
-        <v>566.680961967525</v>
+        <v>680.0171543610298</v>
       </c>
       <c r="D71" t="n">
-        <v>74.09301966433364</v>
+        <v>88.91162359720039</v>
       </c>
       <c r="E71" t="n">
-        <v>62005.07004699383</v>
+        <v>74406.08405639257</v>
       </c>
       <c r="F71" t="n">
-        <v>2922.174921702047</v>
+        <v>3506.609906042457</v>
       </c>
     </row>
     <row r="72">
@@ -1979,16 +1979,16 @@
         <v>1984</v>
       </c>
       <c r="C72" t="n">
-        <v>284.3996301086435</v>
+        <v>341.2795561303722</v>
       </c>
       <c r="D72" t="n">
-        <v>38.83496413517202</v>
+        <v>46.6019569622064</v>
       </c>
       <c r="E72" t="n">
-        <v>28726.57847032741</v>
+        <v>34471.8941643929</v>
       </c>
       <c r="F72" t="n">
-        <v>1332.661505105784</v>
+        <v>1599.193806126941</v>
       </c>
     </row>
     <row r="73">
@@ -2001,16 +2001,16 @@
         <v>1985</v>
       </c>
       <c r="C73" t="n">
-        <v>406.1656193236374</v>
+        <v>487.398743188365</v>
       </c>
       <c r="D73" t="n">
-        <v>81.3090332797937</v>
+        <v>97.57083993575246</v>
       </c>
       <c r="E73" t="n">
-        <v>50644.02456982123</v>
+        <v>60772.82948378551</v>
       </c>
       <c r="F73" t="n">
-        <v>2411.021609094631</v>
+        <v>2893.225930913558</v>
       </c>
     </row>
     <row r="74">
@@ -2023,16 +2023,16 @@
         <v>1986</v>
       </c>
       <c r="C74" t="n">
-        <v>356.8501979797405</v>
+        <v>428.2202375756883</v>
       </c>
       <c r="D74" t="n">
-        <v>81.9450197203229</v>
+        <v>98.3340236643875</v>
       </c>
       <c r="E74" t="n">
-        <v>61447.04517147985</v>
+        <v>73736.45420577582</v>
       </c>
       <c r="F74" t="n">
-        <v>1605.169853396205</v>
+        <v>1926.203824075445</v>
       </c>
     </row>
     <row r="75">
@@ -2045,16 +2045,16 @@
         <v>1987</v>
       </c>
       <c r="C75" t="n">
-        <v>484.3595871408065</v>
+        <v>581.2315045689678</v>
       </c>
       <c r="D75" t="n">
-        <v>64.93396267229987</v>
+        <v>77.92075520675984</v>
       </c>
       <c r="E75" t="n">
-        <v>50933.29155386586</v>
+        <v>61119.94986463903</v>
       </c>
       <c r="F75" t="n">
-        <v>2338.783717194315</v>
+        <v>2806.540460633178</v>
       </c>
     </row>
     <row r="76">
@@ -2067,16 +2067,16 @@
         <v>1988</v>
       </c>
       <c r="C76" t="n">
-        <v>539.9834047188065</v>
+        <v>647.9800856625677</v>
       </c>
       <c r="D76" t="n">
-        <v>109.504828368205</v>
+        <v>131.405794041846</v>
       </c>
       <c r="E76" t="n">
-        <v>86653.45289723207</v>
+        <v>103984.1434766785</v>
       </c>
       <c r="F76" t="n">
-        <v>2570.201277768952</v>
+        <v>3084.241533322742</v>
       </c>
     </row>
     <row r="77">
@@ -2089,16 +2089,16 @@
         <v>1989</v>
       </c>
       <c r="C77" t="n">
-        <v>414.1190643597689</v>
+        <v>496.9428772317227</v>
       </c>
       <c r="D77" t="n">
-        <v>39.58225187455635</v>
+        <v>47.4987022494676</v>
       </c>
       <c r="E77" t="n">
-        <v>35605.60410237641</v>
+        <v>42726.72492285168</v>
       </c>
       <c r="F77" t="n">
-        <v>1326.067173074154</v>
+        <v>1591.280607688984</v>
       </c>
     </row>
     <row r="78">
@@ -2111,16 +2111,16 @@
         <v>1990</v>
       </c>
       <c r="C78" t="n">
-        <v>302.9838621321736</v>
+        <v>363.5806345586084</v>
       </c>
       <c r="D78" t="n">
-        <v>47.06460137069421</v>
+        <v>56.47752164483304</v>
       </c>
       <c r="E78" t="n">
-        <v>45215.23159005932</v>
+        <v>54258.27790807117</v>
       </c>
       <c r="F78" t="n">
-        <v>1145.645864832597</v>
+        <v>1374.775037799116</v>
       </c>
     </row>
     <row r="79">
@@ -2133,16 +2133,16 @@
         <v>1991</v>
       </c>
       <c r="C79" t="n">
-        <v>341.3436820011933</v>
+        <v>409.612418401432</v>
       </c>
       <c r="D79" t="n">
-        <v>32.80097878142183</v>
+        <v>39.36117453770618</v>
       </c>
       <c r="E79" t="n">
-        <v>32123.63860935167</v>
+        <v>38548.36633122201</v>
       </c>
       <c r="F79" t="n">
-        <v>1339.059622727877</v>
+        <v>1606.871547273452</v>
       </c>
     </row>
     <row r="80">
@@ -2155,16 +2155,16 @@
         <v>1992</v>
       </c>
       <c r="C80" t="n">
-        <v>362.7561852658382</v>
+        <v>435.3074223190059</v>
       </c>
       <c r="D80" t="n">
-        <v>47.66631251227864</v>
+        <v>57.19957501473439</v>
       </c>
       <c r="E80" t="n">
-        <v>42373.85759755451</v>
+        <v>50848.62911706541</v>
       </c>
       <c r="F80" t="n">
-        <v>1185.592749195798</v>
+        <v>1422.711299034958</v>
       </c>
     </row>
     <row r="81">
@@ -2177,16 +2177,16 @@
         <v>1993</v>
       </c>
       <c r="C81" t="n">
-        <v>506.6480158402005</v>
+        <v>607.9776190082407</v>
       </c>
       <c r="D81" t="n">
-        <v>35.48317067997471</v>
+        <v>42.57980481596964</v>
       </c>
       <c r="E81" t="n">
-        <v>31575.7481896011</v>
+        <v>37890.89782752132</v>
       </c>
       <c r="F81" t="n">
-        <v>1849.876325252818</v>
+        <v>2219.851590303381</v>
       </c>
     </row>
     <row r="82">
@@ -2199,16 +2199,16 @@
         <v>1994</v>
       </c>
       <c r="C82" t="n">
-        <v>462.2955361264947</v>
+        <v>554.7546433517938</v>
       </c>
       <c r="D82" t="n">
-        <v>38.01437592463345</v>
+        <v>45.61725110956014</v>
       </c>
       <c r="E82" t="n">
-        <v>31960.82002124081</v>
+        <v>38352.98402548897</v>
       </c>
       <c r="F82" t="n">
-        <v>1857.578896033965</v>
+        <v>2229.094675240758</v>
       </c>
     </row>
     <row r="83">
@@ -2221,16 +2221,16 @@
         <v>1995</v>
       </c>
       <c r="C83" t="n">
-        <v>416.163236433764</v>
+        <v>499.3958837205168</v>
       </c>
       <c r="D83" t="n">
-        <v>35.57391873421443</v>
+        <v>42.68870248105732</v>
       </c>
       <c r="E83" t="n">
-        <v>30251.23812447393</v>
+        <v>36301.48574936872</v>
       </c>
       <c r="F83" t="n">
-        <v>1734.724440011734</v>
+        <v>2081.66932801408</v>
       </c>
     </row>
     <row r="84">
@@ -2243,16 +2243,16 @@
         <v>1997</v>
       </c>
       <c r="C84" t="n">
-        <v>329.2517244753072</v>
+        <v>395.1020693703687</v>
       </c>
       <c r="D84" t="n">
-        <v>24.20609031412327</v>
+        <v>29.04730837694792</v>
       </c>
       <c r="E84" t="n">
-        <v>18810.04442771139</v>
+        <v>22572.05331325367</v>
       </c>
       <c r="F84" t="n">
-        <v>1253.812553816466</v>
+        <v>1504.575064579759</v>
       </c>
     </row>
     <row r="85">
@@ -2265,16 +2265,16 @@
         <v>1998</v>
       </c>
       <c r="C85" t="n">
-        <v>342.7841477271845</v>
+        <v>411.3409772726214</v>
       </c>
       <c r="D85" t="n">
-        <v>26.59066683816194</v>
+        <v>31.90880020579433</v>
       </c>
       <c r="E85" t="n">
-        <v>18560.95792223063</v>
+        <v>22273.14950667675</v>
       </c>
       <c r="F85" t="n">
-        <v>2040.042194790369</v>
+        <v>2448.050633748443</v>
       </c>
     </row>
     <row r="86">
@@ -2287,16 +2287,16 @@
         <v>1999</v>
       </c>
       <c r="C86" t="n">
-        <v>414.2876624092112</v>
+        <v>497.1451948910533</v>
       </c>
       <c r="D86" t="n">
-        <v>60.2660302608127</v>
+        <v>72.31923631297521</v>
       </c>
       <c r="E86" t="n">
-        <v>51305.76565226678</v>
+        <v>61566.91878272012</v>
       </c>
       <c r="F86" t="n">
-        <v>2312.399139630359</v>
+        <v>2774.87896755643</v>
       </c>
     </row>
     <row r="87">
@@ -2309,16 +2309,16 @@
         <v>2000</v>
       </c>
       <c r="C87" t="n">
-        <v>577.6106646130205</v>
+        <v>693.1327975356244</v>
       </c>
       <c r="D87" t="n">
-        <v>121.8251126227364</v>
+        <v>146.1901351472836</v>
       </c>
       <c r="E87" t="n">
-        <v>109208.2606153941</v>
+        <v>131049.9127384729</v>
       </c>
       <c r="F87" t="n">
-        <v>3535.884138956621</v>
+        <v>4243.060966747944</v>
       </c>
     </row>
     <row r="88">
@@ -2331,16 +2331,16 @@
         <v>2001</v>
       </c>
       <c r="C88" t="n">
-        <v>332.3919141529207</v>
+        <v>398.8702969835045</v>
       </c>
       <c r="D88" t="n">
-        <v>51.63468978395431</v>
+        <v>61.96162774074515</v>
       </c>
       <c r="E88" t="n">
-        <v>46101.45250349768</v>
+        <v>55321.7430041972</v>
       </c>
       <c r="F88" t="n">
-        <v>1631.147473157248</v>
+        <v>1957.376967788698</v>
       </c>
     </row>
     <row r="89">
@@ -2353,16 +2353,16 @@
         <v>2002</v>
       </c>
       <c r="C89" t="n">
-        <v>304.3574823131871</v>
+        <v>365.2289787758244</v>
       </c>
       <c r="D89" t="n">
-        <v>35.92365335340703</v>
+        <v>43.10838402408844</v>
       </c>
       <c r="E89" t="n">
-        <v>28839.24094632819</v>
+        <v>34607.08913559383</v>
       </c>
       <c r="F89" t="n">
-        <v>1277.333861482351</v>
+        <v>1532.800633778821</v>
       </c>
     </row>
     <row r="90">
@@ -2375,16 +2375,16 @@
         <v>2003</v>
       </c>
       <c r="C90" t="n">
-        <v>452.1123230168666</v>
+        <v>542.5347876202397</v>
       </c>
       <c r="D90" t="n">
-        <v>40.58379084943643</v>
+        <v>48.7005490193237</v>
       </c>
       <c r="E90" t="n">
-        <v>35229.91517588672</v>
+        <v>42275.89821106406</v>
       </c>
       <c r="F90" t="n">
-        <v>1568.157516602377</v>
+        <v>1881.789019922853</v>
       </c>
     </row>
     <row r="91">
@@ -2397,16 +2397,16 @@
         <v>2004</v>
       </c>
       <c r="C91" t="n">
-        <v>359.4880662422953</v>
+        <v>431.3856794907543</v>
       </c>
       <c r="D91" t="n">
-        <v>22.25076980499047</v>
+        <v>26.70092376598855</v>
       </c>
       <c r="E91" t="n">
-        <v>18741.80334734359</v>
+        <v>22490.1640168123</v>
       </c>
       <c r="F91" t="n">
-        <v>1612.508530250801</v>
+        <v>1935.010236300961</v>
       </c>
     </row>
     <row r="92">
@@ -2419,16 +2419,16 @@
         <v>2005</v>
       </c>
       <c r="C92" t="n">
-        <v>251.3456506020084</v>
+        <v>301.6147807224099</v>
       </c>
       <c r="D92" t="n">
-        <v>24.77098244456096</v>
+        <v>29.72517893347314</v>
       </c>
       <c r="E92" t="n">
-        <v>10768.39407969559</v>
+        <v>12922.07289563471</v>
       </c>
       <c r="F92" t="n">
-        <v>1126.502512441475</v>
+        <v>1351.803014929771</v>
       </c>
     </row>
     <row r="93">
@@ -2441,16 +2441,16 @@
         <v>2006</v>
       </c>
       <c r="C93" t="n">
-        <v>574.8447547487186</v>
+        <v>689.8137056984622</v>
       </c>
       <c r="D93" t="n">
-        <v>42.85761690820956</v>
+        <v>51.42914028985146</v>
       </c>
       <c r="E93" t="n">
-        <v>51320.60501735038</v>
+        <v>61584.72602082046</v>
       </c>
       <c r="F93" t="n">
-        <v>3013.609408443519</v>
+        <v>3616.331290132222</v>
       </c>
     </row>
     <row r="94">
@@ -2463,16 +2463,16 @@
         <v>2007</v>
       </c>
       <c r="C94" t="n">
-        <v>237.559270417844</v>
+        <v>285.0711245014127</v>
       </c>
       <c r="D94" t="n">
-        <v>27.87275303564213</v>
+        <v>33.44730364277056</v>
       </c>
       <c r="E94" t="n">
-        <v>28478.41088888189</v>
+        <v>34174.09306665827</v>
       </c>
       <c r="F94" t="n">
-        <v>1394.380755436693</v>
+        <v>1673.256906524032</v>
       </c>
     </row>
     <row r="95">
@@ -2485,16 +2485,16 @@
         <v>2008</v>
       </c>
       <c r="C95" t="n">
-        <v>327.8863722626106</v>
+        <v>393.4636467151325</v>
       </c>
       <c r="D95" t="n">
-        <v>41.3597132309999</v>
+        <v>49.63165587719986</v>
       </c>
       <c r="E95" t="n">
-        <v>32218.54343176986</v>
+        <v>38662.25211812383</v>
       </c>
       <c r="F95" t="n">
-        <v>1964.888253951762</v>
+        <v>2357.865904742113</v>
       </c>
     </row>
     <row r="96">
@@ -2507,10 +2507,10 @@
         <v>2009</v>
       </c>
       <c r="C96" t="n">
-        <v>322.8153840528198</v>
+        <v>387.3784608633839</v>
       </c>
       <c r="D96" t="n">
-        <v>34.43077646749168</v>
+        <v>41.31693176099002</v>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
@@ -2525,10 +2525,10 @@
         <v>2010</v>
       </c>
       <c r="C97" t="n">
-        <v>320.9618714499643</v>
+        <v>385.1542457399573</v>
       </c>
       <c r="D97" t="n">
-        <v>27.32858338055507</v>
+        <v>32.79430005666608</v>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
@@ -2543,16 +2543,16 @@
         <v>2011</v>
       </c>
       <c r="C98" t="n">
-        <v>751.9691337635654</v>
+        <v>902.3629605162783</v>
       </c>
       <c r="D98" t="n">
-        <v>89.47000299547832</v>
+        <v>107.364003594574</v>
       </c>
       <c r="E98" t="n">
-        <v>78308.25325955376</v>
+        <v>93969.90391146451</v>
       </c>
       <c r="F98" t="n">
-        <v>2382.145734972004</v>
+        <v>2858.574881966404</v>
       </c>
     </row>
     <row r="99">
@@ -2565,16 +2565,16 @@
         <v>2012</v>
       </c>
       <c r="C99" t="n">
-        <v>495.09432445008</v>
+        <v>594.1131893400958</v>
       </c>
       <c r="D99" t="n">
-        <v>44.9657178693719</v>
+        <v>53.95886144324627</v>
       </c>
       <c r="E99" t="n">
-        <v>36413.1342291904</v>
+        <v>43695.76107502847</v>
       </c>
       <c r="F99" t="n">
-        <v>2282.921172816922</v>
+        <v>2739.505407380306</v>
       </c>
     </row>
     <row r="100">
@@ -2587,16 +2587,16 @@
         <v>2013</v>
       </c>
       <c r="C100" t="n">
-        <v>431.7371496202156</v>
+        <v>518.0845795442589</v>
       </c>
       <c r="D100" t="n">
-        <v>67.08077632357769</v>
+        <v>80.49693158829325</v>
       </c>
       <c r="E100" t="n">
-        <v>65176.4513132049</v>
+        <v>78211.7415758459</v>
       </c>
       <c r="F100" t="n">
-        <v>2557.487594691125</v>
+        <v>3068.985113629351</v>
       </c>
     </row>
     <row r="101">
@@ -2609,16 +2609,16 @@
         <v>2014</v>
       </c>
       <c r="C101" t="n">
-        <v>476.4685897615743</v>
+        <v>571.7623077138893</v>
       </c>
       <c r="D101" t="n">
-        <v>60.79793318475757</v>
+        <v>72.95751982170908</v>
       </c>
       <c r="E101" t="n">
-        <v>56529.00501292907</v>
+        <v>67834.80601551486</v>
       </c>
       <c r="F101" t="n">
-        <v>3434.547137455055</v>
+        <v>4121.456564946066</v>
       </c>
     </row>
     <row r="102">
@@ -2631,16 +2631,16 @@
         <v>2015</v>
       </c>
       <c r="C102" t="n">
-        <v>538.934422870945</v>
+        <v>646.721307445134</v>
       </c>
       <c r="D102" t="n">
-        <v>34.30324733388102</v>
+        <v>41.16389680065723</v>
       </c>
       <c r="E102" t="n">
-        <v>27469.69566930215</v>
+        <v>32963.63480316258</v>
       </c>
       <c r="F102" t="n">
-        <v>3036.083973188161</v>
+        <v>3643.300767825795</v>
       </c>
     </row>
     <row r="103">
@@ -2653,16 +2653,16 @@
         <v>2016</v>
       </c>
       <c r="C103" t="n">
-        <v>465.9070136391106</v>
+        <v>559.0884163669328</v>
       </c>
       <c r="D103" t="n">
-        <v>79.34766743727867</v>
+        <v>95.21720092473441</v>
       </c>
       <c r="E103" t="n">
-        <v>44027.16048661962</v>
+        <v>52832.5925839435</v>
       </c>
       <c r="F103" t="n">
-        <v>2321.1841192229</v>
+        <v>2785.42094306748</v>
       </c>
     </row>
     <row r="104">
@@ -2675,16 +2675,16 @@
         <v>2017</v>
       </c>
       <c r="C104" t="n">
-        <v>381.109388889494</v>
+        <v>457.3312666673926</v>
       </c>
       <c r="D104" t="n">
-        <v>38.36049217327012</v>
+        <v>46.03259060792413</v>
       </c>
       <c r="E104" t="n">
-        <v>21179.92469217542</v>
+        <v>25415.9096306105</v>
       </c>
       <c r="F104" t="n">
-        <v>2399.826775034355</v>
+        <v>2879.792130041226</v>
       </c>
     </row>
     <row r="105">
@@ -2697,16 +2697,16 @@
         <v>2018</v>
       </c>
       <c r="C105" t="n">
-        <v>408.948859699024</v>
+        <v>490.7386316388289</v>
       </c>
       <c r="D105" t="n">
-        <v>29.09949424452299</v>
+        <v>34.91939309342761</v>
       </c>
       <c r="E105" t="n">
-        <v>25640.08217686556</v>
+        <v>30768.09861223868</v>
       </c>
       <c r="F105" t="n">
-        <v>2162.630923085982</v>
+        <v>2595.157107703178</v>
       </c>
     </row>
     <row r="106">
@@ -2719,16 +2719,16 @@
         <v>2019</v>
       </c>
       <c r="C106" t="n">
-        <v>667.1523390620482</v>
+        <v>800.5828068744581</v>
       </c>
       <c r="D106" t="n">
-        <v>41.47885836606851</v>
+        <v>49.77463003928222</v>
       </c>
       <c r="E106" t="n">
-        <v>28724.45222919917</v>
+        <v>34469.34267503901</v>
       </c>
       <c r="F106" t="n">
-        <v>2767.89143506621</v>
+        <v>3321.46972207945</v>
       </c>
     </row>
     <row r="107">
@@ -2741,16 +2741,16 @@
         <v>2020</v>
       </c>
       <c r="C107" t="n">
-        <v>575.3723040609667</v>
+        <v>690.44676487316</v>
       </c>
       <c r="D107" t="n">
-        <v>38.97760103278343</v>
+        <v>46.77312123934011</v>
       </c>
       <c r="E107" t="n">
-        <v>25748.30982530522</v>
+        <v>30897.97179036626</v>
       </c>
       <c r="F107" t="n">
-        <v>3741.309493374018</v>
+        <v>4489.57139204882</v>
       </c>
     </row>
     <row r="108">
@@ -2763,16 +2763,16 @@
         <v>2021</v>
       </c>
       <c r="C108" t="n">
-        <v>388.1345115319264</v>
+        <v>465.7614138383115</v>
       </c>
       <c r="D108" t="n">
-        <v>24.94532862891623</v>
+        <v>29.93439435469946</v>
       </c>
       <c r="E108" t="n">
-        <v>22017.44991277766</v>
+        <v>26420.9398953332</v>
       </c>
       <c r="F108" t="n">
-        <v>2348.938488757055</v>
+        <v>2818.726186508463</v>
       </c>
     </row>
     <row r="109">
@@ -2785,16 +2785,16 @@
         <v>2022</v>
       </c>
       <c r="C109" t="n">
-        <v>283.826726910645</v>
+        <v>340.592072292774</v>
       </c>
       <c r="D109" t="n">
-        <v>15.42442886732404</v>
+        <v>18.50931464078884</v>
       </c>
       <c r="E109" t="n">
-        <v>11644.94560652335</v>
+        <v>13973.93472782802</v>
       </c>
       <c r="F109" t="n">
-        <v>1411.259649994751</v>
+        <v>1693.511579993701</v>
       </c>
     </row>
     <row r="110">
@@ -2807,16 +2807,16 @@
         <v>2023</v>
       </c>
       <c r="C110" t="n">
-        <v>560.448018572211</v>
+        <v>672.5376222866532</v>
       </c>
       <c r="D110" t="n">
-        <v>62.18970690261032</v>
+        <v>74.62764828313243</v>
       </c>
       <c r="E110" t="n">
-        <v>60876.59215915996</v>
+        <v>73051.91059099195</v>
       </c>
       <c r="F110" t="n">
-        <v>4241.149723654597</v>
+        <v>5089.379668385515</v>
       </c>
     </row>
     <row r="111">
@@ -2829,16 +2829,16 @@
         <v>2024</v>
       </c>
       <c r="C111" t="n">
-        <v>565.0348759788884</v>
+        <v>678.0418511746657</v>
       </c>
       <c r="D111" t="n">
-        <v>102.9710002686016</v>
+        <v>123.565200322322</v>
       </c>
       <c r="E111" t="n">
-        <v>84795.82762133484</v>
+        <v>101754.9931456018</v>
       </c>
       <c r="F111" t="n">
-        <v>4074.471839040365</v>
+        <v>4889.366206848438</v>
       </c>
     </row>
     <row r="112">
@@ -2851,16 +2851,16 @@
         <v>1990</v>
       </c>
       <c r="C112" t="n">
-        <v>96.30059032878843</v>
+        <v>115.5607083945461</v>
       </c>
       <c r="D112" t="n">
-        <v>3.1347203190877</v>
+        <v>3.761664382905239</v>
       </c>
       <c r="E112" t="n">
-        <v>1125.209561750275</v>
+        <v>1350.251474100329</v>
       </c>
       <c r="F112" t="n">
-        <v>374.5739838278247</v>
+        <v>449.4887805933897</v>
       </c>
     </row>
     <row r="113">
@@ -2873,16 +2873,16 @@
         <v>1991</v>
       </c>
       <c r="C113" t="n">
-        <v>188.7482206134084</v>
+        <v>226.4978647360902</v>
       </c>
       <c r="D113" t="n">
-        <v>5.522867764868435</v>
+        <v>6.627441317842122</v>
       </c>
       <c r="E113" t="n">
-        <v>3578.643200174778</v>
+        <v>4294.371840209736</v>
       </c>
       <c r="F113" t="n">
-        <v>520.2077944817898</v>
+        <v>624.249353378148</v>
       </c>
     </row>
     <row r="114">
@@ -2895,16 +2895,16 @@
         <v>1992</v>
       </c>
       <c r="C114" t="n">
-        <v>170.7536891755707</v>
+        <v>204.9044270106848</v>
       </c>
       <c r="D114" t="n">
-        <v>5.391132912906606</v>
+        <v>6.469359495487926</v>
       </c>
       <c r="E114" t="n">
-        <v>3016.063269422176</v>
+        <v>3619.275923306611</v>
       </c>
       <c r="F114" t="n">
-        <v>459.9739111821835</v>
+        <v>551.9686934186202</v>
       </c>
     </row>
     <row r="115">
@@ -2917,16 +2917,16 @@
         <v>1998</v>
       </c>
       <c r="C115" t="n">
-        <v>232.1505511968962</v>
+        <v>278.5806614362754</v>
       </c>
       <c r="D115" t="n">
-        <v>8.431334550740825</v>
+        <v>10.11760146088899</v>
       </c>
       <c r="E115" t="n">
-        <v>3146.030529412534</v>
+        <v>3775.236635295039</v>
       </c>
       <c r="F115" t="n">
-        <v>662.2956777503387</v>
+        <v>794.7548133004062</v>
       </c>
     </row>
     <row r="116">
@@ -2939,13 +2939,13 @@
         <v>1999</v>
       </c>
       <c r="C116" t="n">
-        <v>234.1475415505378</v>
+        <v>280.9770498606454</v>
       </c>
       <c r="D116" t="n">
-        <v>24.47429872815458</v>
+        <v>29.36915847378549</v>
       </c>
       <c r="E116" t="n">
-        <v>19898.39708805639</v>
+        <v>23878.07650566768</v>
       </c>
       <c r="F116" t="inlineStr"/>
     </row>
@@ -2959,16 +2959,16 @@
         <v>2000</v>
       </c>
       <c r="C117" t="n">
-        <v>266.7646031034193</v>
+        <v>320.1175237241032</v>
       </c>
       <c r="D117" t="n">
-        <v>34.21237725447871</v>
+        <v>41.05485270537446</v>
       </c>
       <c r="E117" t="n">
-        <v>24993.56610344455</v>
+        <v>29992.27932413347</v>
       </c>
       <c r="F117" t="n">
-        <v>1493.99805899891</v>
+        <v>1792.797670798693</v>
       </c>
     </row>
     <row r="118">
@@ -2981,16 +2981,16 @@
         <v>2001</v>
       </c>
       <c r="C118" t="n">
-        <v>154.1442611016148</v>
+        <v>184.9731133219378</v>
       </c>
       <c r="D118" t="n">
-        <v>8.572596013177359</v>
+        <v>10.28711521581283</v>
       </c>
       <c r="E118" t="n">
-        <v>5172.394504778814</v>
+        <v>6206.873405734576</v>
       </c>
       <c r="F118" t="n">
-        <v>670.826068318765</v>
+        <v>804.991281982518</v>
       </c>
     </row>
     <row r="119">
@@ -3003,16 +3003,16 @@
         <v>2002</v>
       </c>
       <c r="C119" t="n">
-        <v>159.1984219501458</v>
+        <v>191.038106340175</v>
       </c>
       <c r="D119" t="n">
-        <v>6.946396725855804</v>
+        <v>8.335676071026965</v>
       </c>
       <c r="E119" t="n">
-        <v>2521.484009921179</v>
+        <v>3025.780811905415</v>
       </c>
       <c r="F119" t="n">
-        <v>532.1827648935327</v>
+        <v>638.6193178722393</v>
       </c>
     </row>
     <row r="120">
@@ -3025,16 +3025,16 @@
         <v>2003</v>
       </c>
       <c r="C120" t="n">
-        <v>245.7961613673744</v>
+        <v>294.9553936408491</v>
       </c>
       <c r="D120" t="n">
-        <v>6.342597391154928</v>
+        <v>7.611116869385912</v>
       </c>
       <c r="E120" t="n">
-        <v>3803.393076469351</v>
+        <v>4564.071691763222</v>
       </c>
       <c r="F120" t="n">
-        <v>565.9485319268596</v>
+        <v>679.138238312231</v>
       </c>
     </row>
     <row r="121">
@@ -3047,16 +3047,16 @@
         <v>2004</v>
       </c>
       <c r="C121" t="n">
-        <v>263.4371918655395</v>
+        <v>316.1246302386475</v>
       </c>
       <c r="D121" t="n">
-        <v>23.66753112085047</v>
+        <v>28.40103734502056</v>
       </c>
       <c r="E121" t="n">
-        <v>8309.285390894092</v>
+        <v>9971.142469072911</v>
       </c>
       <c r="F121" t="n">
-        <v>1008.343655808091</v>
+        <v>1210.012386969709</v>
       </c>
     </row>
     <row r="122">
@@ -3069,16 +3069,16 @@
         <v>2005</v>
       </c>
       <c r="C122" t="n">
-        <v>128.9171406727309</v>
+        <v>154.7005688072772</v>
       </c>
       <c r="D122" t="n">
-        <v>6.468861752526793</v>
+        <v>7.762634103032152</v>
       </c>
       <c r="E122" t="n">
-        <v>3656.207449077632</v>
+        <v>4387.448938893157</v>
       </c>
       <c r="F122" t="n">
-        <v>452.3613927363837</v>
+        <v>542.8336712836602</v>
       </c>
     </row>
     <row r="123">
@@ -3091,16 +3091,16 @@
         <v>2006</v>
       </c>
       <c r="C123" t="n">
-        <v>351.9950641189254</v>
+        <v>422.3940769427105</v>
       </c>
       <c r="D123" t="n">
-        <v>18.35656707511707</v>
+        <v>22.02788049014049</v>
       </c>
       <c r="E123" t="n">
-        <v>11023.05360549697</v>
+        <v>13227.66432659636</v>
       </c>
       <c r="F123" t="n">
-        <v>2259.156924488845</v>
+        <v>2710.988309386613</v>
       </c>
     </row>
     <row r="124">
@@ -3113,16 +3113,16 @@
         <v>2009</v>
       </c>
       <c r="C124" t="n">
-        <v>137.4472703415738</v>
+        <v>164.9367244098886</v>
       </c>
       <c r="D124" t="n">
-        <v>7.689058737469397</v>
+        <v>9.226870484963278</v>
       </c>
       <c r="E124" t="n">
-        <v>3475.014570021169</v>
+        <v>4170.017484025402</v>
       </c>
       <c r="F124" t="n">
-        <v>520.2069387554491</v>
+        <v>624.248326506539</v>
       </c>
     </row>
     <row r="125">
@@ -3135,16 +3135,16 @@
         <v>2011</v>
       </c>
       <c r="C125" t="n">
-        <v>212.3295263975157</v>
+        <v>254.7954316770188</v>
       </c>
       <c r="D125" t="n">
-        <v>15.18756626046809</v>
+        <v>18.22507951256171</v>
       </c>
       <c r="E125" t="n">
-        <v>6400.493102258798</v>
+        <v>7680.591722710556</v>
       </c>
       <c r="F125" t="n">
-        <v>843.0628354560022</v>
+        <v>1011.675402547202</v>
       </c>
     </row>
     <row r="126">
@@ -3157,16 +3157,16 @@
         <v>2012</v>
       </c>
       <c r="C126" t="n">
-        <v>268.5067090561985</v>
+        <v>322.2080508674381</v>
       </c>
       <c r="D126" t="n">
-        <v>14.19344039642769</v>
+        <v>17.03212847571321</v>
       </c>
       <c r="E126" t="n">
-        <v>3426.105041662815</v>
+        <v>4111.326049995378</v>
       </c>
       <c r="F126" t="n">
-        <v>796.7050088705156</v>
+        <v>956.0460106446188</v>
       </c>
     </row>
     <row r="127">
@@ -3179,16 +3179,16 @@
         <v>2017</v>
       </c>
       <c r="C127" t="n">
-        <v>135.554170737</v>
+        <v>162.6650048844</v>
       </c>
       <c r="D127" t="n">
-        <v>11.5394454923256</v>
+        <v>13.84733459079072</v>
       </c>
       <c r="E127" t="n">
-        <v>6569.0057028033</v>
+        <v>7882.80684336396</v>
       </c>
       <c r="F127" t="n">
-        <v>863.3668779925355</v>
+        <v>1036.040253591042</v>
       </c>
     </row>
     <row r="128">
@@ -3201,16 +3201,16 @@
         <v>2018</v>
       </c>
       <c r="C128" t="n">
-        <v>146.497039981418</v>
+        <v>175.7964479777016</v>
       </c>
       <c r="D128" t="n">
-        <v>3.990346537679242</v>
+        <v>4.788415845215092</v>
       </c>
       <c r="E128" t="n">
-        <v>1407.632318777788</v>
+        <v>1689.158782533345</v>
       </c>
       <c r="F128" t="n">
-        <v>772.6897498289139</v>
+        <v>927.2276997946969</v>
       </c>
     </row>
     <row r="129">
@@ -3223,16 +3223,16 @@
         <v>2019</v>
       </c>
       <c r="C129" t="n">
-        <v>426.7653124438379</v>
+        <v>512.1183749326054</v>
       </c>
       <c r="D129" t="n">
-        <v>12.19365225820236</v>
+        <v>14.63238270984283</v>
       </c>
       <c r="E129" t="n">
-        <v>5633.275478811207</v>
+        <v>6759.930574573445</v>
       </c>
       <c r="F129" t="n">
-        <v>1267.076277201774</v>
+        <v>1520.491532642129</v>
       </c>
     </row>
     <row r="130">
@@ -3245,16 +3245,16 @@
         <v>2020</v>
       </c>
       <c r="C130" t="n">
-        <v>284.4395916951127</v>
+        <v>341.3275100341353</v>
       </c>
       <c r="D130" t="n">
-        <v>27.68865602462944</v>
+        <v>33.22638722955534</v>
       </c>
       <c r="E130" t="n">
-        <v>16963.77749967664</v>
+        <v>20356.53299961197</v>
       </c>
       <c r="F130" t="n">
-        <v>1794.387261036246</v>
+        <v>2153.264713243496</v>
       </c>
     </row>
     <row r="131">
@@ -3267,16 +3267,16 @@
         <v>2021</v>
       </c>
       <c r="C131" t="n">
-        <v>213.9853593863128</v>
+        <v>256.7824312635754</v>
       </c>
       <c r="D131" t="n">
-        <v>12.29523769813772</v>
+        <v>14.75428523776526</v>
       </c>
       <c r="E131" t="n">
-        <v>8216.38013517173</v>
+        <v>9859.65616220608</v>
       </c>
       <c r="F131" t="n">
-        <v>888.8435230427676</v>
+        <v>1066.612227651321</v>
       </c>
     </row>
     <row r="132">
@@ -3289,16 +3289,16 @@
         <v>2022</v>
       </c>
       <c r="C132" t="n">
-        <v>97.94413690590241</v>
+        <v>117.5329642870828</v>
       </c>
       <c r="D132" t="n">
-        <v>2.802323087615671</v>
+        <v>3.362787705138804</v>
       </c>
       <c r="E132" t="n">
-        <v>1175.472025974233</v>
+        <v>1410.56643116908</v>
       </c>
       <c r="F132" t="n">
-        <v>451.5671326251716</v>
+        <v>541.880559150206</v>
       </c>
     </row>
     <row r="133">
@@ -3311,16 +3311,16 @@
         <v>2023</v>
       </c>
       <c r="C133" t="n">
-        <v>221.8208376890288</v>
+        <v>266.1850052268346</v>
       </c>
       <c r="D133" t="n">
-        <v>16.19098995094127</v>
+        <v>19.42918794112952</v>
       </c>
       <c r="E133" t="n">
-        <v>12331.1799082945</v>
+        <v>14797.4158899534</v>
       </c>
       <c r="F133" t="n">
-        <v>1404.633278212553</v>
+        <v>1685.559933855064</v>
       </c>
     </row>
     <row r="134">
@@ -3333,16 +3333,16 @@
         <v>2024</v>
       </c>
       <c r="C134" t="n">
-        <v>147.2043919809193</v>
+        <v>176.6452703771032</v>
       </c>
       <c r="D134" t="n">
-        <v>11.88498836698347</v>
+        <v>14.26198604038017</v>
       </c>
       <c r="E134" t="n">
-        <v>6260.091120177674</v>
+        <v>7512.109344213212</v>
       </c>
       <c r="F134" t="n">
-        <v>904.3010673921951</v>
+        <v>1085.161280870634</v>
       </c>
     </row>
     <row r="135">
@@ -3356,13 +3356,13 @@
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="n">
-        <v>0.6967264591711987</v>
+        <v>0.8360717510054383</v>
       </c>
       <c r="E135" t="n">
-        <v>256.0970839333807</v>
+        <v>307.3165007200568</v>
       </c>
       <c r="F135" t="n">
-        <v>48.69397214070364</v>
+        <v>58.43276656884436</v>
       </c>
     </row>
     <row r="136">
@@ -3375,16 +3375,16 @@
         <v>1999</v>
       </c>
       <c r="C136" t="n">
-        <v>23.97374007275566</v>
+        <v>28.76848808730679</v>
       </c>
       <c r="D136" t="n">
-        <v>0.8174197563361036</v>
+        <v>0.9809037076033242</v>
       </c>
       <c r="E136" t="n">
-        <v>664.0109360370595</v>
+        <v>796.8131232444716</v>
       </c>
       <c r="F136" t="n">
-        <v>62.46817933055838</v>
+        <v>74.96181519667006</v>
       </c>
     </row>
     <row r="137">
@@ -3397,13 +3397,13 @@
         <v>2000</v>
       </c>
       <c r="C137" t="n">
-        <v>20.33711044847003</v>
+        <v>24.40453253816403</v>
       </c>
       <c r="D137" t="n">
-        <v>1.096397749324903</v>
+        <v>1.315677299189884</v>
       </c>
       <c r="E137" t="n">
-        <v>551.6928578761639</v>
+        <v>662.0314294513969</v>
       </c>
       <c r="F137" t="inlineStr"/>
     </row>
@@ -3417,13 +3417,13 @@
         <v>2001</v>
       </c>
       <c r="C138" t="n">
-        <v>13.38740161784559</v>
+        <v>16.0648819414147</v>
       </c>
       <c r="D138" t="n">
-        <v>0.64395849664145</v>
+        <v>0.7727501959697397</v>
       </c>
       <c r="E138" t="n">
-        <v>239.2491092769994</v>
+        <v>287.0989311323991</v>
       </c>
       <c r="F138" t="inlineStr"/>
     </row>
@@ -3437,13 +3437,13 @@
         <v>2002</v>
       </c>
       <c r="C139" t="n">
-        <v>8.920319976661778</v>
+        <v>10.70438397199414</v>
       </c>
       <c r="D139" t="n">
-        <v>0.3530571651294602</v>
+        <v>0.4236685981553523</v>
       </c>
       <c r="E139" t="n">
-        <v>161.6162371029338</v>
+        <v>193.9394845235206</v>
       </c>
       <c r="F139" t="inlineStr"/>
     </row>
@@ -3457,13 +3457,13 @@
         <v>2003</v>
       </c>
       <c r="C140" t="n">
-        <v>15.42985673434066</v>
+        <v>18.51582808120879</v>
       </c>
       <c r="D140" t="n">
-        <v>0.5202906395277737</v>
+        <v>0.6243487674333283</v>
       </c>
       <c r="E140" t="n">
-        <v>303.8446502119068</v>
+        <v>364.6135802542881</v>
       </c>
       <c r="F140" t="inlineStr"/>
     </row>
@@ -3477,16 +3477,16 @@
         <v>2004</v>
       </c>
       <c r="C141" t="n">
-        <v>16.73129092940139</v>
+        <v>20.07754911528168</v>
       </c>
       <c r="D141" t="n">
-        <v>0.5666966876343265</v>
+        <v>0.6800360251611918</v>
       </c>
       <c r="E141" t="n">
-        <v>300.6225891685597</v>
+        <v>360.7471070022716</v>
       </c>
       <c r="F141" t="n">
-        <v>33.18904022160527</v>
+        <v>39.8268482659263</v>
       </c>
     </row>
     <row r="142">
@@ -3499,16 +3499,16 @@
         <v>2005</v>
       </c>
       <c r="C142" t="n">
-        <v>9.532769886034693</v>
+        <v>11.43932386324163</v>
       </c>
       <c r="D142" t="n">
-        <v>0.4201206249353536</v>
+        <v>0.5041447499224242</v>
       </c>
       <c r="E142" t="n">
-        <v>331.3035819661915</v>
+        <v>397.5642983594295</v>
       </c>
       <c r="F142" t="n">
-        <v>22.77757451894387</v>
+        <v>27.33308942273264</v>
       </c>
     </row>
     <row r="143">
@@ -3521,13 +3521,13 @@
         <v>2006</v>
       </c>
       <c r="C143" t="n">
-        <v>22.89720856445912</v>
+        <v>27.47665027735095</v>
       </c>
       <c r="D143" t="n">
-        <v>1.267521800983396</v>
+        <v>1.521026161180075</v>
       </c>
       <c r="E143" t="n">
-        <v>1031.152707628628</v>
+        <v>1237.383249154354</v>
       </c>
       <c r="F143" t="inlineStr"/>
     </row>
@@ -3541,16 +3541,16 @@
         <v>2011</v>
       </c>
       <c r="C144" t="n">
-        <v>14.77923881261369</v>
+        <v>17.73508657513642</v>
       </c>
       <c r="D144" t="n">
-        <v>0.9103647065827822</v>
+        <v>1.092437647899339</v>
       </c>
       <c r="E144" t="n">
-        <v>528.8377829631823</v>
+        <v>634.6053395558189</v>
       </c>
       <c r="F144" t="n">
-        <v>51.23300545699406</v>
+        <v>61.47960654839287</v>
       </c>
     </row>
     <row r="145">
@@ -3563,16 +3563,16 @@
         <v>2012</v>
       </c>
       <c r="C145" t="n">
-        <v>15.96029042303256</v>
+        <v>19.15234850763907</v>
       </c>
       <c r="D145" t="n">
-        <v>0.4282373880286872</v>
+        <v>0.5138848656344245</v>
       </c>
       <c r="E145" t="n">
-        <v>193.8772028633419</v>
+        <v>232.6526434360104</v>
       </c>
       <c r="F145" t="n">
-        <v>55.34818106173935</v>
+        <v>66.41781727408723</v>
       </c>
     </row>
     <row r="146">
@@ -3585,16 +3585,16 @@
         <v>2013</v>
       </c>
       <c r="C146" t="n">
-        <v>10.4719797860435</v>
+        <v>12.5663757432522</v>
       </c>
       <c r="D146" t="n">
-        <v>1.253225645828915</v>
+        <v>1.503870774994698</v>
       </c>
       <c r="E146" t="n">
-        <v>966.9861441338189</v>
+        <v>1160.383372960583</v>
       </c>
       <c r="F146" t="n">
-        <v>65.00929877296122</v>
+        <v>78.01115852755343</v>
       </c>
     </row>
     <row r="147">
@@ -3607,16 +3607,16 @@
         <v>2014</v>
       </c>
       <c r="C147" t="n">
-        <v>15.66342971472917</v>
+        <v>18.796115657675</v>
       </c>
       <c r="D147" t="n">
-        <v>0.9791915177608516</v>
+        <v>1.175029821313021</v>
       </c>
       <c r="E147" t="n">
-        <v>699.1844647077061</v>
+        <v>839.0213576492474</v>
       </c>
       <c r="F147" t="n">
-        <v>100.1414218444871</v>
+        <v>120.1697062133845</v>
       </c>
     </row>
     <row r="148">
@@ -3629,16 +3629,16 @@
         <v>2015</v>
       </c>
       <c r="C148" t="n">
-        <v>14.59327701163174</v>
+        <v>17.5119324139581</v>
       </c>
       <c r="D148" t="n">
-        <v>0.6775456860608734</v>
+        <v>0.8130548232730483</v>
       </c>
       <c r="E148" t="n">
-        <v>419.1733788617973</v>
+        <v>503.0080546341568</v>
       </c>
       <c r="F148" t="n">
-        <v>80.60445597392822</v>
+        <v>96.72534716871388</v>
       </c>
     </row>
     <row r="149">
@@ -3651,16 +3651,16 @@
         <v>2016</v>
       </c>
       <c r="C149" t="n">
-        <v>9.756235006538578</v>
+        <v>11.70748200784629</v>
       </c>
       <c r="D149" t="n">
-        <v>0.9443920269385722</v>
+        <v>1.133270432326287</v>
       </c>
       <c r="E149" t="n">
-        <v>250.5892148403428</v>
+        <v>300.7070578084114</v>
       </c>
       <c r="F149" t="n">
-        <v>63.37160775859282</v>
+        <v>76.04592931031137</v>
       </c>
     </row>
     <row r="150">
@@ -3673,16 +3673,16 @@
         <v>2018</v>
       </c>
       <c r="C150" t="n">
-        <v>15.67346995040358</v>
+        <v>18.80816394048429</v>
       </c>
       <c r="D150" t="n">
-        <v>0.4462839525840797</v>
+        <v>0.5355407431008957</v>
       </c>
       <c r="E150" t="n">
-        <v>269.2312658257636</v>
+        <v>323.0775189909162</v>
       </c>
       <c r="F150" t="n">
-        <v>60.91200159074388</v>
+        <v>73.09440190889266</v>
       </c>
     </row>
     <row r="151">
@@ -3695,16 +3695,16 @@
         <v>2019</v>
       </c>
       <c r="C151" t="n">
-        <v>28.93660473343259</v>
+        <v>34.72392568011911</v>
       </c>
       <c r="D151" t="n">
-        <v>1.43739550275823</v>
+        <v>1.724874603309876</v>
       </c>
       <c r="E151" t="n">
-        <v>776.0854103613681</v>
+        <v>931.3024924336419</v>
       </c>
       <c r="F151" t="n">
-        <v>84.3493768756538</v>
+        <v>101.2192522507846</v>
       </c>
     </row>
     <row r="152">
@@ -3717,16 +3717,16 @@
         <v>2020</v>
       </c>
       <c r="C152" t="n">
-        <v>22.76835184088262</v>
+        <v>27.32202220905914</v>
       </c>
       <c r="D152" t="n">
-        <v>0.8009809356693804</v>
+        <v>0.9611771228032562</v>
       </c>
       <c r="E152" t="n">
-        <v>315.5125163713641</v>
+        <v>378.6150196456369</v>
       </c>
       <c r="F152" t="n">
-        <v>98.35708933618547</v>
+        <v>118.0285072034226</v>
       </c>
     </row>
     <row r="153">
@@ -3739,10 +3739,10 @@
         <v>2021</v>
       </c>
       <c r="C153" t="n">
-        <v>10.92032540636314</v>
+        <v>13.10439048763576</v>
       </c>
       <c r="D153" t="n">
-        <v>0.5296290134050547</v>
+        <v>0.6355548160860655</v>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
@@ -3757,14 +3757,14 @@
         <v>2022</v>
       </c>
       <c r="C154" t="n">
-        <v>5.356980573241867</v>
+        <v>6.428376687890241</v>
       </c>
       <c r="D154" t="n">
-        <v>0.1730526177275885</v>
+        <v>0.2076631412731063</v>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="n">
-        <v>25.29710789923476</v>
+        <v>30.35652947908171</v>
       </c>
     </row>
     <row r="155">
@@ -3777,16 +3777,16 @@
         <v>2023</v>
       </c>
       <c r="C155" t="n">
-        <v>13.22150521603742</v>
+        <v>15.8658062592449</v>
       </c>
       <c r="D155" t="n">
-        <v>0.6262761540827471</v>
+        <v>0.7515313848992965</v>
       </c>
       <c r="E155" t="n">
-        <v>321.9176944223065</v>
+        <v>386.3012333067678</v>
       </c>
       <c r="F155" t="n">
-        <v>74.84248794751281</v>
+        <v>89.8109855370154</v>
       </c>
     </row>
     <row r="156">
@@ -3799,16 +3799,16 @@
         <v>2024</v>
       </c>
       <c r="C156" t="n">
-        <v>12.21280575266457</v>
+        <v>14.65536690319749</v>
       </c>
       <c r="D156" t="n">
-        <v>0.6916929418938628</v>
+        <v>0.8300315302726354</v>
       </c>
       <c r="E156" t="n">
-        <v>259.1484440333675</v>
+        <v>310.9781328400411</v>
       </c>
       <c r="F156" t="n">
-        <v>44.69026978043336</v>
+        <v>53.62832373652004</v>
       </c>
     </row>
     <row r="157">
@@ -3821,16 +3821,16 @@
         <v>2011</v>
       </c>
       <c r="C157" t="n">
-        <v>66.38607914391281</v>
+        <v>79.66329497269535</v>
       </c>
       <c r="D157" t="n">
-        <v>4.341972262161554</v>
+        <v>5.210366714593865</v>
       </c>
       <c r="E157" t="n">
-        <v>2088.514946557186</v>
+        <v>2506.217935868624</v>
       </c>
       <c r="F157" t="n">
-        <v>767.7107731494013</v>
+        <v>921.2529277792815</v>
       </c>
     </row>
     <row r="158">
@@ -3843,16 +3843,16 @@
         <v>2017</v>
       </c>
       <c r="C158" t="n">
-        <v>44.8936129068021</v>
+        <v>53.87233548816253</v>
       </c>
       <c r="D158" t="n">
-        <v>1.954405618927778</v>
+        <v>2.345286742713334</v>
       </c>
       <c r="E158" t="n">
-        <v>777.1116220338538</v>
+        <v>932.5339464406246</v>
       </c>
       <c r="F158" t="n">
-        <v>535.2481834166693</v>
+        <v>642.2978201000033</v>
       </c>
     </row>
     <row r="159">
@@ -3865,16 +3865,16 @@
         <v>2018</v>
       </c>
       <c r="C159" t="n">
-        <v>86.83469252730305</v>
+        <v>104.2016310327637</v>
       </c>
       <c r="D159" t="n">
-        <v>2.262049442825004</v>
+        <v>2.714459331390005</v>
       </c>
       <c r="E159" t="n">
-        <v>1034.116445823784</v>
+        <v>1240.93973498854</v>
       </c>
       <c r="F159" t="n">
-        <v>687.4153924254158</v>
+        <v>824.898470910499</v>
       </c>
     </row>
     <row r="160">
@@ -3887,16 +3887,16 @@
         <v>2019</v>
       </c>
       <c r="C160" t="n">
-        <v>125.1386320365314</v>
+        <v>150.1663584438377</v>
       </c>
       <c r="D160" t="n">
-        <v>3.209373962109245</v>
+        <v>3.851248754531093</v>
       </c>
       <c r="E160" t="n">
-        <v>1430.425260367964</v>
+        <v>1716.510312441556</v>
       </c>
       <c r="F160" t="n">
-        <v>894.9443693340589</v>
+        <v>1073.933243200871</v>
       </c>
     </row>
     <row r="161">
@@ -3909,16 +3909,16 @@
         <v>2020</v>
       </c>
       <c r="C161" t="n">
-        <v>112.0509340255936</v>
+        <v>134.4611208307123</v>
       </c>
       <c r="D161" t="n">
-        <v>5.951949792042934</v>
+        <v>7.142339750451521</v>
       </c>
       <c r="E161" t="n">
-        <v>2406.153437801333</v>
+        <v>2887.3841253616</v>
       </c>
       <c r="F161" t="n">
-        <v>1159.623918140276</v>
+        <v>1391.548701768331</v>
       </c>
     </row>
     <row r="162">
@@ -3931,16 +3931,16 @@
         <v>2021</v>
       </c>
       <c r="C162" t="n">
-        <v>70.85285233604257</v>
+        <v>85.02342280325111</v>
       </c>
       <c r="D162" t="n">
-        <v>5.819299083564566</v>
+        <v>6.983158900277481</v>
       </c>
       <c r="E162" t="n">
-        <v>4342.626134634939</v>
+        <v>5211.151361561927</v>
       </c>
       <c r="F162" t="n">
-        <v>618.4678202867691</v>
+        <v>742.161384344123</v>
       </c>
     </row>
     <row r="163">
@@ -3953,16 +3953,16 @@
         <v>2022</v>
       </c>
       <c r="C163" t="n">
-        <v>29.55536871821249</v>
+        <v>35.46644246185499</v>
       </c>
       <c r="D163" t="n">
-        <v>0.9418902462964645</v>
+        <v>1.130268295555757</v>
       </c>
       <c r="E163" t="n">
-        <v>257.7373332608099</v>
+        <v>309.2847999129718</v>
       </c>
       <c r="F163" t="n">
-        <v>316.4601505206385</v>
+        <v>379.7521806247662</v>
       </c>
     </row>
     <row r="164">
@@ -3975,16 +3975,16 @@
         <v>2023</v>
       </c>
       <c r="C164" t="n">
-        <v>79.04849943667686</v>
+        <v>94.85819932401222</v>
       </c>
       <c r="D164" t="n">
-        <v>5.42516676621531</v>
+        <v>6.51020011945837</v>
       </c>
       <c r="E164" t="n">
-        <v>3716.23140989222</v>
+        <v>4459.477691870663</v>
       </c>
       <c r="F164" t="n">
-        <v>996.6481057834178</v>
+        <v>1195.977726940101</v>
       </c>
     </row>
     <row r="165">
@@ -3997,16 +3997,16 @@
         <v>2024</v>
       </c>
       <c r="C165" t="n">
-        <v>65.48904761237107</v>
+        <v>78.58685713484529</v>
       </c>
       <c r="D165" t="n">
-        <v>3.410732739865195</v>
+        <v>4.092879287838233</v>
       </c>
       <c r="E165" t="n">
-        <v>3021.983780843507</v>
+        <v>3626.380537012208</v>
       </c>
       <c r="F165" t="n">
-        <v>538.1144434946913</v>
+        <v>645.7373321936294</v>
       </c>
     </row>
     <row r="166">
@@ -4019,16 +4019,16 @@
         <v>2017</v>
       </c>
       <c r="C166" t="n">
-        <v>7.601158086872602</v>
+        <v>9.12138970424712</v>
       </c>
       <c r="D166" t="n">
-        <v>0.2963878509855383</v>
+        <v>0.3556654211826459</v>
       </c>
       <c r="E166" t="n">
-        <v>85.01488980970291</v>
+        <v>102.0178677716435</v>
       </c>
       <c r="F166" t="n">
-        <v>105.7514152496175</v>
+        <v>126.901698299541</v>
       </c>
     </row>
     <row r="167">
@@ -4041,16 +4041,16 @@
         <v>2018</v>
       </c>
       <c r="C167" t="n">
-        <v>12.03966443157236</v>
+        <v>14.44759731788683</v>
       </c>
       <c r="D167" t="n">
-        <v>0.3228871252526269</v>
+        <v>0.3874645503031524</v>
       </c>
       <c r="E167" t="n">
-        <v>147.4724929738897</v>
+        <v>176.9669915686676</v>
       </c>
       <c r="F167" t="n">
-        <v>132.1199194463231</v>
+        <v>158.5439033355878</v>
       </c>
     </row>
     <row r="168">
@@ -4063,16 +4063,16 @@
         <v>2019</v>
       </c>
       <c r="C168" t="n">
-        <v>15.61902044698713</v>
+        <v>18.74282453638455</v>
       </c>
       <c r="D168" t="n">
-        <v>0.5149084598850812</v>
+        <v>0.6178901518620976</v>
       </c>
       <c r="E168" t="n">
-        <v>220.4319626434661</v>
+        <v>264.5183551721593</v>
       </c>
       <c r="F168" t="n">
-        <v>194.6953311163847</v>
+        <v>233.6343973396616</v>
       </c>
     </row>
     <row r="169">
@@ -4085,16 +4085,16 @@
         <v>2020</v>
       </c>
       <c r="C169" t="n">
-        <v>18.06037046155562</v>
+        <v>21.67244455386674</v>
       </c>
       <c r="D169" t="n">
-        <v>1.09065538318044</v>
+        <v>1.308786459816528</v>
       </c>
       <c r="E169" t="n">
-        <v>302.743561619997</v>
+        <v>363.2922739439961</v>
       </c>
       <c r="F169" t="n">
-        <v>260.8764771218694</v>
+        <v>313.0517725462432</v>
       </c>
     </row>
     <row r="170">
@@ -4107,16 +4107,16 @@
         <v>2021</v>
       </c>
       <c r="C170" t="n">
-        <v>11.79403990597149</v>
+        <v>14.15284788716578</v>
       </c>
       <c r="D170" t="n">
-        <v>0.3631692425541906</v>
+        <v>0.4358030910650287</v>
       </c>
       <c r="E170" t="n">
-        <v>131.4454693391129</v>
+        <v>157.7345632069356</v>
       </c>
       <c r="F170" t="n">
-        <v>138.0941476993935</v>
+        <v>165.7129772392721</v>
       </c>
     </row>
     <row r="171">
@@ -4129,16 +4129,16 @@
         <v>2022</v>
       </c>
       <c r="C171" t="n">
-        <v>4.782860546340594</v>
+        <v>5.739432655608712</v>
       </c>
       <c r="D171" t="n">
-        <v>0.1536386177739167</v>
+        <v>0.1843663413287001</v>
       </c>
       <c r="E171" t="n">
-        <v>39.90007417307307</v>
+        <v>47.88008900768768</v>
       </c>
       <c r="F171" t="n">
-        <v>67.37068842282663</v>
+        <v>80.84482610739195</v>
       </c>
     </row>
     <row r="172">
@@ -4151,16 +4151,16 @@
         <v>2023</v>
       </c>
       <c r="C172" t="n">
-        <v>12.53667710179156</v>
+        <v>15.04401252214987</v>
       </c>
       <c r="D172" t="n">
-        <v>0.532714311779416</v>
+        <v>0.6392571741352991</v>
       </c>
       <c r="E172" t="n">
-        <v>416.7633724753818</v>
+        <v>500.1160469704582</v>
       </c>
       <c r="F172" t="n">
-        <v>192.2738714805733</v>
+        <v>230.7286457766881</v>
       </c>
     </row>
     <row r="173">
@@ -4173,16 +4173,16 @@
         <v>2024</v>
       </c>
       <c r="C173" t="n">
-        <v>11.67748012668895</v>
+        <v>14.01297615202673</v>
       </c>
       <c r="D173" t="n">
-        <v>0.4438024184046431</v>
+        <v>0.5325629020855717</v>
       </c>
       <c r="E173" t="n">
-        <v>179.7720933857473</v>
+        <v>215.7265120628967</v>
       </c>
       <c r="F173" t="n">
-        <v>159.2615338242494</v>
+        <v>191.1138405890993</v>
       </c>
     </row>
   </sheetData>
@@ -4276,13 +4276,13 @@
         <v>0.2168604205660558</v>
       </c>
       <c r="G2" t="n">
-        <v>1.883447101247998</v>
+        <v>2.26013652149758</v>
       </c>
       <c r="H2" t="n">
-        <v>4.762377242521692</v>
+        <v>5.714852691026019</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8951767848272653</v>
+        <v>-1.074212141792748</v>
       </c>
     </row>
     <row r="3">
@@ -4315,13 +4315,13 @@
         <v>0.1671450946627271</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3724214950219225</v>
+        <v>-0.446905794026307</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1198883955539755</v>
+        <v>0.1438660746647707</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8857823499676581</v>
+        <v>-1.06293881996119</v>
       </c>
     </row>
     <row r="4">
@@ -4354,13 +4354,13 @@
         <v>0.08988158946826497</v>
       </c>
       <c r="G4" t="n">
-        <v>-317.810944761693</v>
+        <v>-381.3731337140309</v>
       </c>
       <c r="H4" t="n">
-        <v>42.85301614458415</v>
+        <v>51.42361937350021</v>
       </c>
       <c r="I4" t="n">
-        <v>-801.1078755674507</v>
+        <v>-961.3294506809426</v>
       </c>
     </row>
     <row r="5">
@@ -4393,13 +4393,13 @@
         <v>0.005814073275163256</v>
       </c>
       <c r="G5" t="n">
-        <v>32.33834151298702</v>
+        <v>38.8060098155844</v>
       </c>
       <c r="H5" t="n">
-        <v>51.24228234776216</v>
+        <v>61.49073881731465</v>
       </c>
       <c r="I5" t="n">
-        <v>7.667461913262908</v>
+        <v>9.200954295915501</v>
       </c>
     </row>
     <row r="6">
@@ -4432,13 +4432,13 @@
         <v>0.9015386266571279</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.04960865528737364</v>
+        <v>-0.05953038634484983</v>
       </c>
       <c r="H6" t="n">
-        <v>3.447309790174177</v>
+        <v>4.136771748209011</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.841231119921354</v>
+        <v>-2.209477343905624</v>
       </c>
     </row>
     <row r="7">
@@ -4471,13 +4471,13 @@
         <v>0.5361867719001741</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01842394837541621</v>
+        <v>0.02210873805049945</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1450819003153632</v>
+        <v>0.1740982803784358</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1204232807037215</v>
+        <v>-0.1445079368444659</v>
       </c>
     </row>
     <row r="8">
@@ -4510,13 +4510,13 @@
         <v>0.5361867719001741</v>
       </c>
       <c r="G8" t="n">
-        <v>14.82280902510891</v>
+        <v>17.78737083013067</v>
       </c>
       <c r="H8" t="n">
-        <v>72.57622393676469</v>
+        <v>87.09146872411755</v>
       </c>
       <c r="I8" t="n">
-        <v>-44.49324665217658</v>
+        <v>-53.39189598261184</v>
       </c>
     </row>
     <row r="9">
@@ -4549,13 +4549,13 @@
         <v>0.7105230229164894</v>
       </c>
       <c r="G9" t="n">
-        <v>5.789698885636511</v>
+        <v>6.947638662763817</v>
       </c>
       <c r="H9" t="n">
-        <v>45.94542270071138</v>
+        <v>55.13450724085367</v>
       </c>
       <c r="I9" t="n">
-        <v>-28.30059170849562</v>
+        <v>-33.96071005019476</v>
       </c>
     </row>
     <row r="10">
@@ -4588,13 +4588,13 @@
         <v>0.7115714636761059</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7909426076260999</v>
+        <v>0.9491311291513114</v>
       </c>
       <c r="H10" t="n">
-        <v>4.060210804269357</v>
+        <v>4.872252965123232</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.513297319862212</v>
+        <v>-3.015956783834657</v>
       </c>
     </row>
     <row r="11">
@@ -4627,13 +4627,13 @@
         <v>0.3417178800455669</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1635847863991987</v>
+        <v>0.1963017436790388</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3333788183147761</v>
+        <v>0.4000545819777312</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2109114109211075</v>
+        <v>-0.253093693105328</v>
       </c>
     </row>
     <row r="12">
@@ -4666,13 +4666,13 @@
         <v>0.3155727359639027</v>
       </c>
       <c r="G12" t="n">
-        <v>90.46210317416353</v>
+        <v>108.5545238089963</v>
       </c>
       <c r="H12" t="n">
-        <v>228.747437852305</v>
+        <v>274.4969254227661</v>
       </c>
       <c r="I12" t="n">
-        <v>-77.52165078066274</v>
+        <v>-93.02598093679535</v>
       </c>
     </row>
     <row r="13">
@@ -4705,13 +4705,13 @@
         <v>0.02784675596413333</v>
       </c>
       <c r="G13" t="n">
-        <v>14.72111908454115</v>
+        <v>17.66534290144933</v>
       </c>
       <c r="H13" t="n">
-        <v>27.63829636658636</v>
+        <v>33.16595563990364</v>
       </c>
       <c r="I13" t="n">
-        <v>3.543119269015623</v>
+        <v>4.251743122818753</v>
       </c>
     </row>
     <row r="14">
@@ -4744,13 +4744,13 @@
         <v>0.7544541774940892</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.67258676300787</v>
+        <v>-2.007104115609447</v>
       </c>
       <c r="H14" t="n">
-        <v>6.489809857310117</v>
+        <v>7.787771828772145</v>
       </c>
       <c r="I14" t="n">
-        <v>-11.92991688483206</v>
+        <v>-14.31590026179847</v>
       </c>
     </row>
     <row r="15">
@@ -4783,13 +4783,13 @@
         <v>0.7544541774940892</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1189994454057238</v>
+        <v>0.1427993344868685</v>
       </c>
       <c r="H15" t="n">
-        <v>0.947324519284241</v>
+        <v>1.136789423141088</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3090983650786445</v>
+        <v>-0.3709180380943735</v>
       </c>
     </row>
     <row r="16">
@@ -4822,13 +4822,13 @@
         <v>0.2514521865080219</v>
       </c>
       <c r="G16" t="n">
-        <v>287.6582639425192</v>
+        <v>345.1899167310229</v>
       </c>
       <c r="H16" t="n">
-        <v>571.4515373810641</v>
+        <v>685.7418448572769</v>
       </c>
       <c r="I16" t="n">
-        <v>-166.4343284814888</v>
+        <v>-199.7211941777866</v>
       </c>
     </row>
     <row r="17">
@@ -4861,13 +4861,13 @@
         <v>0.9169652366288645</v>
       </c>
       <c r="G17" t="n">
-        <v>-13.19753198055915</v>
+        <v>-15.83703837667097</v>
       </c>
       <c r="H17" t="n">
-        <v>110.8271464870264</v>
+        <v>132.9925757844316</v>
       </c>
       <c r="I17" t="n">
-        <v>-71.36598516787353</v>
+        <v>-85.63918220144831</v>
       </c>
     </row>
     <row r="18">
@@ -4900,13 +4900,13 @@
         <v>0.9062974979468705</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2347502116161878</v>
+        <v>0.2817002539394301</v>
       </c>
       <c r="H18" t="n">
-        <v>3.545903393500504</v>
+        <v>4.255084072200583</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.746035010221934</v>
+        <v>-4.495242012266324</v>
       </c>
     </row>
     <row r="19">
@@ -4939,13 +4939,13 @@
         <v>0.2894224860302206</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.09133445919416053</v>
+        <v>-0.1096013510329925</v>
       </c>
       <c r="H19" t="n">
-        <v>0.08512232052205072</v>
+        <v>0.1021467846264608</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3149886351474135</v>
+        <v>-0.3779863621768961</v>
       </c>
     </row>
     <row r="20">
@@ -4978,13 +4978,13 @@
         <v>0.05704160286357429</v>
       </c>
       <c r="G20" t="n">
-        <v>-45.20836854787304</v>
+        <v>-54.25004225744756</v>
       </c>
       <c r="H20" t="n">
-        <v>4.97070140196347</v>
+        <v>5.964841682356123</v>
       </c>
       <c r="I20" t="n">
-        <v>-95.81561464105089</v>
+        <v>-114.9787375692613</v>
       </c>
     </row>
     <row r="21">
@@ -5017,13 +5017,13 @@
         <v>0.002858749184990295</v>
       </c>
       <c r="G21" t="n">
-        <v>36.37964969031034</v>
+        <v>43.65557962837244</v>
       </c>
       <c r="H21" t="n">
-        <v>53.27666810701471</v>
+        <v>63.93200172841765</v>
       </c>
       <c r="I21" t="n">
-        <v>12.9874209828632</v>
+        <v>15.5849051794357</v>
       </c>
     </row>
     <row r="22">
@@ -5056,13 +5056,13 @@
         <v>0.8865048064138312</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0374985130240321</v>
+        <v>0.04499821562883769</v>
       </c>
       <c r="H22" t="n">
-        <v>0.655279015466559</v>
+        <v>0.7863348185598708</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5187109729654754</v>
+        <v>-0.6224531675585713</v>
       </c>
     </row>
     <row r="23">
@@ -5095,13 +5095,13 @@
         <v>0.2389927879015219</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01792759546280634</v>
+        <v>0.02151311455536763</v>
       </c>
       <c r="H23" t="n">
-        <v>0.05175760893966993</v>
+        <v>0.06210913072760387</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.01233332230560929</v>
+        <v>-0.01479998676673117</v>
       </c>
     </row>
     <row r="24">
@@ -5134,13 +5134,13 @@
         <v>0.5206932698330875</v>
       </c>
       <c r="G24" t="n">
-        <v>4.750227955774964</v>
+        <v>5.700273546929941</v>
       </c>
       <c r="H24" t="n">
-        <v>18.06240754969724</v>
+        <v>21.67488905963668</v>
       </c>
       <c r="I24" t="n">
-        <v>-9.205803072052731</v>
+        <v>-11.04696368646326</v>
       </c>
     </row>
     <row r="25">
@@ -5173,13 +5173,13 @@
         <v>0.004164806898991236</v>
       </c>
       <c r="G25" t="n">
-        <v>7.799121896608805</v>
+        <v>9.35894627593056</v>
       </c>
       <c r="H25" t="n">
-        <v>12.22626692080429</v>
+        <v>14.67152030496515</v>
       </c>
       <c r="I25" t="n">
-        <v>2.632752504685588</v>
+        <v>3.159303005622701</v>
       </c>
     </row>
     <row r="26">
@@ -5212,13 +5212,13 @@
         <v>0.2905607553787695</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.174819222310143</v>
+        <v>-0.2097830667721721</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1391837194768101</v>
+        <v>0.1670204633721721</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4957876948297167</v>
+        <v>-0.5949452337956591</v>
       </c>
     </row>
     <row r="27">
@@ -5251,13 +5251,13 @@
         <v>0.8215254231894769</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.002042307879211621</v>
+        <v>-0.002450769455053927</v>
       </c>
       <c r="H27" t="n">
-        <v>0.01464276550219087</v>
+        <v>0.01757131860262903</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.02242408947208864</v>
+        <v>-0.02690890736650636</v>
       </c>
     </row>
     <row r="28">
@@ -5290,13 +5290,13 @@
         <v>0.8203382164336168</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8105977526122026</v>
+        <v>0.9727173031346548</v>
       </c>
       <c r="H28" t="n">
-        <v>10.77734451756706</v>
+        <v>12.93281342108048</v>
       </c>
       <c r="I28" t="n">
-        <v>-13.34317328815222</v>
+        <v>-16.01180794578266</v>
       </c>
     </row>
     <row r="29">
@@ -5329,13 +5329,13 @@
         <v>0.2241343019601669</v>
       </c>
       <c r="G29" t="n">
-        <v>1.090874159702638</v>
+        <v>1.309048991643165</v>
       </c>
       <c r="H29" t="n">
-        <v>3.215465606486463</v>
+        <v>3.858558727783756</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.7202460033019271</v>
+        <v>-0.8642952039623104</v>
       </c>
     </row>
   </sheetData>

--- a/data/annual_loads_waterbodies.xlsx
+++ b/data/annual_loads_waterbodies.xlsx
@@ -480,7 +480,7 @@
         <v>516.6387494041873</v>
       </c>
       <c r="F2" t="n">
-        <v>212.2622864804887</v>
+        <v>217.4736289185775</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>1996</v>
       </c>
       <c r="C3" t="n">
-        <v>50.79570443575703</v>
+        <v>51.32869255300714</v>
       </c>
       <c r="D3" t="n">
         <v>1.302319497896878</v>
@@ -581,13 +581,13 @@
         <v>2000</v>
       </c>
       <c r="C7" t="n">
-        <v>76.17669645769872</v>
+        <v>81.08685298733415</v>
       </c>
       <c r="D7" t="n">
         <v>4.575242451471255</v>
       </c>
       <c r="E7" t="n">
-        <v>1381.698713502394</v>
+        <v>1516.492426408186</v>
       </c>
       <c r="F7" t="n">
         <v>514.5068887583486</v>
@@ -779,7 +779,7 @@
         <v>2009</v>
       </c>
       <c r="C16" t="n">
-        <v>37.48639639122129</v>
+        <v>42.663871831362</v>
       </c>
       <c r="D16" t="n">
         <v>1.305194352529113</v>
@@ -824,7 +824,7 @@
         <v>65.22493830832144</v>
       </c>
       <c r="D18" t="n">
-        <v>3.3926087300932</v>
+        <v>3.459787513354118</v>
       </c>
       <c r="E18" t="n">
         <v>1273.576617839817</v>
@@ -846,10 +846,10 @@
         <v>57.73145889096433</v>
       </c>
       <c r="D19" t="n">
-        <v>2.986800182977315</v>
+        <v>3.16725936433042</v>
       </c>
       <c r="E19" t="n">
-        <v>1025.167856743108</v>
+        <v>1115.050563144609</v>
       </c>
       <c r="F19" t="n">
         <v>341.0640154150917</v>
@@ -991,13 +991,13 @@
         <v>2019</v>
       </c>
       <c r="C26" t="n">
-        <v>82.92215653174877</v>
+        <v>85.29118087354188</v>
       </c>
       <c r="D26" t="n">
-        <v>3.255860284971044</v>
+        <v>3.531486866937927</v>
       </c>
       <c r="E26" t="n">
-        <v>1048.734593461281</v>
+        <v>1154.317411956237</v>
       </c>
       <c r="F26" t="n">
         <v>524.4754086238461</v>
@@ -1057,7 +1057,7 @@
         <v>2022</v>
       </c>
       <c r="C29" t="n">
-        <v>35.68757472396414</v>
+        <v>44.82956253058431</v>
       </c>
       <c r="D29" t="n">
         <v>1.387517839144506</v>
@@ -1191,7 +1191,7 @@
         <v>40.53987019922116</v>
       </c>
       <c r="E35" t="n">
-        <v>4638.379582476791</v>
+        <v>15526.71588886437</v>
       </c>
       <c r="F35" t="inlineStr"/>
     </row>
@@ -1253,7 +1253,7 @@
         <v>12.63927178839586</v>
       </c>
       <c r="E38" t="n">
-        <v>4226.681035363031</v>
+        <v>4460.441339471327</v>
       </c>
       <c r="F38" t="n">
         <v>1044.896885386453</v>
@@ -1449,7 +1449,7 @@
         <v>17.79439531362919</v>
       </c>
       <c r="E47" t="n">
-        <v>4857.854172248018</v>
+        <v>6204.300176263578</v>
       </c>
       <c r="F47" t="n">
         <v>1320.302739733719</v>
@@ -1493,10 +1493,10 @@
         <v>37.23347712024713</v>
       </c>
       <c r="E49" t="n">
-        <v>12662.98955300256</v>
+        <v>17073.01088071766</v>
       </c>
       <c r="F49" t="n">
-        <v>3093.434614512265</v>
+        <v>3114.422018139068</v>
       </c>
     </row>
     <row r="50">
@@ -1515,7 +1515,7 @@
         <v>25.53768851400098</v>
       </c>
       <c r="E50" t="n">
-        <v>5079.111135390028</v>
+        <v>18626.20105913134</v>
       </c>
       <c r="F50" t="n">
         <v>1772.998760300929</v>
@@ -1581,7 +1581,7 @@
         <v>9.483917002062677</v>
       </c>
       <c r="E53" t="n">
-        <v>1533.86967553231</v>
+        <v>1932.576317173651</v>
       </c>
       <c r="F53" t="n">
         <v>1327.408651990087</v>
@@ -1711,7 +1711,7 @@
         <v>13.12749136781718</v>
       </c>
       <c r="E59" t="n">
-        <v>3509.772114256197</v>
+        <v>4949.73144092061</v>
       </c>
       <c r="F59" t="n">
         <v>1819.587265486208</v>
@@ -1857,7 +1857,7 @@
         <v>42.29584113665814</v>
       </c>
       <c r="E66" t="n">
-        <v>10363.41480161733</v>
+        <v>12420.38028177709</v>
       </c>
       <c r="F66" t="n">
         <v>3912.438718568309</v>
@@ -1920,10 +1920,10 @@
         <v>378.1589914881386</v>
       </c>
       <c r="D69" t="n">
-        <v>68.58965574845983</v>
+        <v>77.23012861196472</v>
       </c>
       <c r="E69" t="n">
-        <v>40085.49150276944</v>
+        <v>72430.98231784237</v>
       </c>
       <c r="F69" t="inlineStr"/>
     </row>
@@ -1940,10 +1940,10 @@
         <v>498.4401972865416</v>
       </c>
       <c r="D70" t="n">
-        <v>76.78197093992893</v>
+        <v>81.79679491468778</v>
       </c>
       <c r="E70" t="n">
-        <v>67376.9089255424</v>
+        <v>76150.60621244203</v>
       </c>
       <c r="F70" t="inlineStr"/>
     </row>
@@ -1960,7 +1960,7 @@
         <v>680.0171543610298</v>
       </c>
       <c r="D71" t="n">
-        <v>88.91162359720039</v>
+        <v>112.0990135300667</v>
       </c>
       <c r="E71" t="n">
         <v>74406.08405639257</v>
@@ -1982,10 +1982,10 @@
         <v>341.2795561303722</v>
       </c>
       <c r="D72" t="n">
-        <v>46.6019569622064</v>
+        <v>64.84876015498823</v>
       </c>
       <c r="E72" t="n">
-        <v>34471.8941643929</v>
+        <v>42395.93027510954</v>
       </c>
       <c r="F72" t="n">
         <v>1599.193806126941</v>
@@ -2007,7 +2007,7 @@
         <v>97.57083993575246</v>
       </c>
       <c r="E73" t="n">
-        <v>60772.82948378551</v>
+        <v>70217.98248564792</v>
       </c>
       <c r="F73" t="n">
         <v>2893.225930913558</v>
@@ -2026,10 +2026,10 @@
         <v>428.2202375756883</v>
       </c>
       <c r="D74" t="n">
-        <v>98.3340236643875</v>
+        <v>120.840076459736</v>
       </c>
       <c r="E74" t="n">
-        <v>73736.45420577582</v>
+        <v>91179.01893851414</v>
       </c>
       <c r="F74" t="n">
         <v>1926.203824075445</v>
@@ -2048,10 +2048,10 @@
         <v>581.2315045689678</v>
       </c>
       <c r="D75" t="n">
-        <v>77.92075520675984</v>
+        <v>84.81144317249569</v>
       </c>
       <c r="E75" t="n">
-        <v>61119.94986463903</v>
+        <v>66155.01911483545</v>
       </c>
       <c r="F75" t="n">
         <v>2806.540460633178</v>
@@ -2070,10 +2070,10 @@
         <v>647.9800856625677</v>
       </c>
       <c r="D76" t="n">
-        <v>131.405794041846</v>
+        <v>136.4081961201191</v>
       </c>
       <c r="E76" t="n">
-        <v>103984.1434766785</v>
+        <v>115108.0960529657</v>
       </c>
       <c r="F76" t="n">
         <v>3084.241533322742</v>
@@ -2092,7 +2092,7 @@
         <v>496.9428772317227</v>
       </c>
       <c r="D77" t="n">
-        <v>47.4987022494676</v>
+        <v>52.64133725501354</v>
       </c>
       <c r="E77" t="n">
         <v>42726.72492285168</v>
@@ -2114,10 +2114,10 @@
         <v>363.5806345586084</v>
       </c>
       <c r="D78" t="n">
-        <v>56.47752164483304</v>
+        <v>77.06137896074759</v>
       </c>
       <c r="E78" t="n">
-        <v>54258.27790807117</v>
+        <v>78815.56668574465</v>
       </c>
       <c r="F78" t="n">
         <v>1374.775037799116</v>
@@ -2158,7 +2158,7 @@
         <v>435.3074223190059</v>
       </c>
       <c r="D80" t="n">
-        <v>57.19957501473439</v>
+        <v>57.90286252782821</v>
       </c>
       <c r="E80" t="n">
         <v>50848.62911706541</v>
@@ -2180,13 +2180,13 @@
         <v>607.9776190082407</v>
       </c>
       <c r="D81" t="n">
-        <v>42.57980481596964</v>
+        <v>44.92995065420201</v>
       </c>
       <c r="E81" t="n">
         <v>37890.89782752132</v>
       </c>
       <c r="F81" t="n">
-        <v>2219.851590303381</v>
+        <v>3074.799355095129</v>
       </c>
     </row>
     <row r="82">
@@ -2312,10 +2312,10 @@
         <v>693.1327975356244</v>
       </c>
       <c r="D87" t="n">
-        <v>146.1901351472836</v>
+        <v>152.3691745116093</v>
       </c>
       <c r="E87" t="n">
-        <v>131049.9127384729</v>
+        <v>135822.1119202853</v>
       </c>
       <c r="F87" t="n">
         <v>4243.060966747944</v>
@@ -2334,10 +2334,10 @@
         <v>398.8702969835045</v>
       </c>
       <c r="D88" t="n">
-        <v>61.96162774074515</v>
+        <v>66.07838379068764</v>
       </c>
       <c r="E88" t="n">
-        <v>55321.7430041972</v>
+        <v>59529.87678280933</v>
       </c>
       <c r="F88" t="n">
         <v>1957.376967788698</v>
@@ -2359,7 +2359,7 @@
         <v>43.10838402408844</v>
       </c>
       <c r="E89" t="n">
-        <v>34607.08913559383</v>
+        <v>39556.58090614752</v>
       </c>
       <c r="F89" t="n">
         <v>1532.800633778821</v>
@@ -2444,7 +2444,7 @@
         <v>689.8137056984622</v>
       </c>
       <c r="D93" t="n">
-        <v>51.42914028985146</v>
+        <v>75.99166872619867</v>
       </c>
       <c r="E93" t="n">
         <v>61584.72602082046</v>
@@ -2546,7 +2546,7 @@
         <v>902.3629605162783</v>
       </c>
       <c r="D98" t="n">
-        <v>107.364003594574</v>
+        <v>135.9654901092225</v>
       </c>
       <c r="E98" t="n">
         <v>93969.90391146451</v>
@@ -2659,7 +2659,7 @@
         <v>95.21720092473441</v>
       </c>
       <c r="E103" t="n">
-        <v>52832.5925839435</v>
+        <v>102437.5985193932</v>
       </c>
       <c r="F103" t="n">
         <v>2785.42094306748</v>
@@ -2681,7 +2681,7 @@
         <v>46.03259060792413</v>
       </c>
       <c r="E104" t="n">
-        <v>25415.9096306105</v>
+        <v>46665.58136984465</v>
       </c>
       <c r="F104" t="n">
         <v>2879.792130041226</v>
@@ -2816,7 +2816,7 @@
         <v>73051.91059099195</v>
       </c>
       <c r="F110" t="n">
-        <v>5089.379668385515</v>
+        <v>5622.641959700421</v>
       </c>
     </row>
     <row r="111">
@@ -2876,10 +2876,10 @@
         <v>226.4978647360902</v>
       </c>
       <c r="D113" t="n">
-        <v>6.627441317842122</v>
+        <v>9.61461428113558</v>
       </c>
       <c r="E113" t="n">
-        <v>4294.371840209736</v>
+        <v>6994.710453654764</v>
       </c>
       <c r="F113" t="n">
         <v>624.249353378148</v>
@@ -3009,7 +3009,7 @@
         <v>8.335676071026965</v>
       </c>
       <c r="E119" t="n">
-        <v>3025.780811905415</v>
+        <v>4844.077617883121</v>
       </c>
       <c r="F119" t="n">
         <v>638.6193178722393</v>
@@ -3053,7 +3053,7 @@
         <v>28.40103734502056</v>
       </c>
       <c r="E121" t="n">
-        <v>9971.142469072911</v>
+        <v>22012.96040062487</v>
       </c>
       <c r="F121" t="n">
         <v>1210.012386969709</v>
@@ -3091,7 +3091,7 @@
         <v>2006</v>
       </c>
       <c r="C123" t="n">
-        <v>422.3940769427105</v>
+        <v>484.3160162116932</v>
       </c>
       <c r="D123" t="n">
         <v>22.02788049014049</v>
@@ -3251,7 +3251,7 @@
         <v>33.22638722955534</v>
       </c>
       <c r="E130" t="n">
-        <v>20356.53299961197</v>
+        <v>21919.18137863137</v>
       </c>
       <c r="F130" t="n">
         <v>2153.264713243496</v>
@@ -3339,7 +3339,7 @@
         <v>14.26198604038017</v>
       </c>
       <c r="E134" t="n">
-        <v>7512.109344213212</v>
+        <v>10465.04919787375</v>
       </c>
       <c r="F134" t="n">
         <v>1085.161280870634</v>
@@ -3354,7 +3354,9 @@
       <c r="B135" t="n">
         <v>1998</v>
       </c>
-      <c r="C135" t="inlineStr"/>
+      <c r="C135" t="n">
+        <v>35.22436430541052</v>
+      </c>
       <c r="D135" t="n">
         <v>0.8360717510054383</v>
       </c>
@@ -3400,10 +3402,10 @@
         <v>24.40453253816403</v>
       </c>
       <c r="D137" t="n">
-        <v>1.315677299189884</v>
+        <v>2.117917297767146</v>
       </c>
       <c r="E137" t="n">
-        <v>662.0314294513969</v>
+        <v>1467.389834988821</v>
       </c>
       <c r="F137" t="inlineStr"/>
     </row>
@@ -3420,10 +3422,10 @@
         <v>16.0648819414147</v>
       </c>
       <c r="D138" t="n">
-        <v>0.7727501959697397</v>
+        <v>0.9231749372119721</v>
       </c>
       <c r="E138" t="n">
-        <v>287.0989311323991</v>
+        <v>401.5961903902409</v>
       </c>
       <c r="F138" t="inlineStr"/>
     </row>
@@ -3544,10 +3546,10 @@
         <v>17.73508657513642</v>
       </c>
       <c r="D144" t="n">
-        <v>1.092437647899339</v>
+        <v>2.016574622946294</v>
       </c>
       <c r="E144" t="n">
-        <v>634.6053395558189</v>
+        <v>1602.590247699093</v>
       </c>
       <c r="F144" t="n">
         <v>61.47960654839287</v>
@@ -3654,10 +3656,10 @@
         <v>11.70748200784629</v>
       </c>
       <c r="D149" t="n">
-        <v>1.133270432326287</v>
+        <v>1.454344307776128</v>
       </c>
       <c r="E149" t="n">
-        <v>300.7070578084114</v>
+        <v>1297.381876102844</v>
       </c>
       <c r="F149" t="n">
         <v>76.04592931031137</v>
@@ -3887,7 +3889,7 @@
         <v>2019</v>
       </c>
       <c r="C160" t="n">
-        <v>150.1663584438377</v>
+        <v>136.7539067600311</v>
       </c>
       <c r="D160" t="n">
         <v>3.851248754531093</v>
@@ -3912,10 +3914,10 @@
         <v>134.4611208307123</v>
       </c>
       <c r="D161" t="n">
-        <v>7.142339750451521</v>
+        <v>10.23642935095861</v>
       </c>
       <c r="E161" t="n">
-        <v>2887.3841253616</v>
+        <v>5531.287031060498</v>
       </c>
       <c r="F161" t="n">
         <v>1391.548701768331</v>
@@ -4000,7 +4002,7 @@
         <v>78.58685713484529</v>
       </c>
       <c r="D165" t="n">
-        <v>4.092879287838233</v>
+        <v>4.22096550429413</v>
       </c>
       <c r="E165" t="n">
         <v>3626.380537012208</v>
@@ -4063,7 +4065,7 @@
         <v>2019</v>
       </c>
       <c r="C168" t="n">
-        <v>18.74282453638455</v>
+        <v>18.78688124727843</v>
       </c>
       <c r="D168" t="n">
         <v>0.6178901518620976</v>
@@ -4091,7 +4093,7 @@
         <v>1.308786459816528</v>
       </c>
       <c r="E169" t="n">
-        <v>363.2922739439961</v>
+        <v>749.0986577889029</v>
       </c>
       <c r="F169" t="n">
         <v>313.0517725462432</v>
@@ -4110,10 +4112,10 @@
         <v>14.15284788716578</v>
       </c>
       <c r="D170" t="n">
-        <v>0.4358030910650287</v>
+        <v>0.5389119407391477</v>
       </c>
       <c r="E170" t="n">
-        <v>157.7345632069356</v>
+        <v>214.1688182808587</v>
       </c>
       <c r="F170" t="n">
         <v>165.7129772392721</v>
@@ -4157,7 +4159,7 @@
         <v>0.6392571741352991</v>
       </c>
       <c r="E172" t="n">
-        <v>500.1160469704582</v>
+        <v>510.9200881859394</v>
       </c>
       <c r="F172" t="n">
         <v>230.7286457766881</v>
@@ -4176,13 +4178,13 @@
         <v>14.01297615202673</v>
       </c>
       <c r="D173" t="n">
-        <v>0.5325629020855717</v>
+        <v>0.6693222158990653</v>
       </c>
       <c r="E173" t="n">
         <v>215.7265120628967</v>
       </c>
       <c r="F173" t="n">
-        <v>191.1138405890993</v>
+        <v>195.5887791075585</v>
       </c>
     </row>
   </sheetData>
@@ -4312,16 +4314,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.1671450946627271</v>
+        <v>0.05681822931485225</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.446905794026307</v>
+        <v>-0.7138617998550546</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1438660746647707</v>
+        <v>0.01805823905930397</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.06293881996119</v>
+        <v>-1.432259895096275</v>
       </c>
     </row>
     <row r="4">
@@ -4351,16 +4353,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.08988158946826497</v>
+        <v>0.0638436989206157</v>
       </c>
       <c r="G4" t="n">
-        <v>-381.3731337140309</v>
+        <v>-532.6316209273488</v>
       </c>
       <c r="H4" t="n">
-        <v>51.42361937350021</v>
+        <v>24.60413403172788</v>
       </c>
       <c r="I4" t="n">
-        <v>-961.3294506809426</v>
+        <v>-1229.156479641246</v>
       </c>
     </row>
     <row r="5">
@@ -4390,16 +4392,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.005814073275163256</v>
+        <v>0.01107437281616974</v>
       </c>
       <c r="G5" t="n">
-        <v>38.8060098155844</v>
+        <v>37.86135639566405</v>
       </c>
       <c r="H5" t="n">
-        <v>61.49073881731465</v>
+        <v>60.632630544393</v>
       </c>
       <c r="I5" t="n">
-        <v>9.200954295915501</v>
+        <v>6.974659534164441</v>
       </c>
     </row>
     <row r="6">
@@ -4468,13 +4470,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.5361867719001741</v>
+        <v>0.2655103889538737</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02210873805049945</v>
+        <v>0.04413910262544479</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1740982803784358</v>
+        <v>0.2304256015589452</v>
       </c>
       <c r="I7" t="n">
         <v>-0.1445079368444659</v>
@@ -4510,13 +4512,13 @@
         <v>0.5361867719001741</v>
       </c>
       <c r="G8" t="n">
-        <v>17.78737083013067</v>
+        <v>14.32235047283566</v>
       </c>
       <c r="H8" t="n">
-        <v>87.09146872411755</v>
+        <v>87.55136360349167</v>
       </c>
       <c r="I8" t="n">
-        <v>-53.39189598261184</v>
+        <v>-79.39285653432115</v>
       </c>
     </row>
     <row r="9">
@@ -4549,10 +4551,10 @@
         <v>0.7105230229164894</v>
       </c>
       <c r="G9" t="n">
-        <v>6.947638662763817</v>
+        <v>7.93848284846395</v>
       </c>
       <c r="H9" t="n">
-        <v>55.13450724085367</v>
+        <v>57.37197650008329</v>
       </c>
       <c r="I9" t="n">
         <v>-33.96071005019476</v>
@@ -4591,7 +4593,7 @@
         <v>0.9491311291513114</v>
       </c>
       <c r="H10" t="n">
-        <v>4.872252965123232</v>
+        <v>4.701286981629579</v>
       </c>
       <c r="I10" t="n">
         <v>-3.015956783834657</v>
@@ -4624,16 +4626,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.3417178800455669</v>
+        <v>0.4596078230489589</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1963017436790388</v>
+        <v>0.1627969349867363</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4000545819777312</v>
+        <v>0.3811676406768105</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.253093693105328</v>
+        <v>-0.2588144939937264</v>
       </c>
     </row>
     <row r="12">
@@ -4663,16 +4665,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.3155727359639027</v>
+        <v>0.4922895298178107</v>
       </c>
       <c r="G12" t="n">
-        <v>108.5545238089963</v>
+        <v>87.4589005140168</v>
       </c>
       <c r="H12" t="n">
-        <v>274.4969254227661</v>
+        <v>268.0822859933359</v>
       </c>
       <c r="I12" t="n">
-        <v>-93.02598093679535</v>
+        <v>-175.1107357484751</v>
       </c>
     </row>
     <row r="13">
@@ -4747,10 +4749,10 @@
         <v>-2.007104115609447</v>
       </c>
       <c r="H14" t="n">
-        <v>7.787771828772145</v>
+        <v>7.136326473416968</v>
       </c>
       <c r="I14" t="n">
-        <v>-14.31590026179847</v>
+        <v>-13.20097383556671</v>
       </c>
     </row>
     <row r="15">
@@ -4789,7 +4791,7 @@
         <v>1.136789423141088</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3709180380943735</v>
+        <v>-0.4775133286467552</v>
       </c>
     </row>
     <row r="16">
@@ -4819,16 +4821,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.2514521865080219</v>
+        <v>0.6021675277481957</v>
       </c>
       <c r="G16" t="n">
-        <v>345.1899167310229</v>
+        <v>289.4495655586229</v>
       </c>
       <c r="H16" t="n">
         <v>685.7418448572769</v>
       </c>
       <c r="I16" t="n">
-        <v>-199.7211941777866</v>
+        <v>-320.1356694985707</v>
       </c>
     </row>
     <row r="17">
@@ -4975,16 +4977,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.05704160286357429</v>
+        <v>0.07824219874308347</v>
       </c>
       <c r="G20" t="n">
-        <v>-54.25004225744756</v>
+        <v>-69.26780295870621</v>
       </c>
       <c r="H20" t="n">
-        <v>5.964841682356123</v>
+        <v>10.96226035007863</v>
       </c>
       <c r="I20" t="n">
-        <v>-114.9787375692613</v>
+        <v>-136.0914998271753</v>
       </c>
     </row>
     <row r="21">
@@ -5053,16 +5055,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.8865048064138312</v>
+        <v>0.7481053914270006</v>
       </c>
       <c r="G22" t="n">
-        <v>0.04499821562883769</v>
+        <v>0.1374811663549445</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7863348185598708</v>
+        <v>0.7441654612608859</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6224531675585713</v>
+        <v>-0.4775340659607014</v>
       </c>
     </row>
     <row r="23">
@@ -5092,16 +5094,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.2389927879015219</v>
+        <v>0.2117118319412423</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02151311455536763</v>
+        <v>0.0218681131362306</v>
       </c>
       <c r="H23" t="n">
-        <v>0.06210913072760387</v>
+        <v>0.06376835757875088</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.01479998676673117</v>
+        <v>-0.01275880990492734</v>
       </c>
     </row>
     <row r="24">
@@ -5137,10 +5139,10 @@
         <v>5.700273546929941</v>
       </c>
       <c r="H24" t="n">
-        <v>21.67488905963668</v>
+        <v>23.68467715206089</v>
       </c>
       <c r="I24" t="n">
-        <v>-11.04696368646326</v>
+        <v>-11.53220793306063</v>
       </c>
     </row>
     <row r="25">
@@ -5170,16 +5172,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.004164806898991236</v>
+        <v>0.004782669315397836</v>
       </c>
       <c r="G25" t="n">
-        <v>9.35894627593056</v>
+        <v>9.282071767869864</v>
       </c>
       <c r="H25" t="n">
-        <v>14.67152030496515</v>
+        <v>14.60383702754566</v>
       </c>
       <c r="I25" t="n">
-        <v>3.159303005622701</v>
+        <v>2.785257145737035</v>
       </c>
     </row>
     <row r="26">
@@ -5209,16 +5211,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.2905607553787695</v>
+        <v>0.1143167755404042</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2097830667721721</v>
+        <v>-0.2987765680358331</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1670204633721721</v>
+        <v>0.0716498597037252</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5949452337956591</v>
+        <v>-0.7122935207863031</v>
       </c>
     </row>
     <row r="27">
@@ -5248,16 +5250,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.8215254231894769</v>
+        <v>0.5727823105937271</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.002450769455053927</v>
+        <v>-0.007690429796718981</v>
       </c>
       <c r="H27" t="n">
-        <v>0.01757131860262903</v>
+        <v>0.01847104236896741</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.02690890736650636</v>
+        <v>-0.03838859060596889</v>
       </c>
     </row>
     <row r="28">
@@ -5287,16 +5289,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.8203382164336168</v>
+        <v>0.9741177473553713</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9727173031346548</v>
+        <v>-0.6604755791175183</v>
       </c>
       <c r="H28" t="n">
-        <v>12.93281342108048</v>
+        <v>15.07081259248431</v>
       </c>
       <c r="I28" t="n">
-        <v>-16.01180794578266</v>
+        <v>-23.55880784620273</v>
       </c>
     </row>
     <row r="29">
